--- a/data/arbeidsfiler/weekly_results_2026.xlsx
+++ b/data/arbeidsfiler/weekly_results_2026.xlsx
@@ -26291,11 +26291,7 @@
       <c r="N253" t="n">
         <v>5</v>
       </c>
-      <c r="O253" t="inlineStr">
-        <is>
-          <t>Netto 16:05</t>
-        </is>
-      </c>
+      <c r="O253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
           <t>Fredrikstadløpet 5 km manuell registrering fra bilde</t>
@@ -26388,11 +26384,7 @@
       <c r="N254" t="n">
         <v>56</v>
       </c>
-      <c r="O254" t="inlineStr">
-        <is>
-          <t>Netto 20:55</t>
-        </is>
-      </c>
+      <c r="O254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
           <t>Fredrikstadløpet 5 km manuell registrering fra bilde</t>
@@ -26485,11 +26477,7 @@
       <c r="N255" t="n">
         <v>116</v>
       </c>
-      <c r="O255" t="inlineStr">
-        <is>
-          <t>Netto 25:25</t>
-        </is>
-      </c>
+      <c r="O255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
           <t>Fredrikstadløpet 5 km manuell registrering fra bilde</t>
@@ -26580,11 +26568,7 @@
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr"/>
       <c r="N256" t="inlineStr"/>
-      <c r="O256" t="inlineStr">
-        <is>
-          <t>Manuell registrering fra tekst. BIB 14445. NC.</t>
-        </is>
-      </c>
+      <c r="O256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
           <t>Milano Marathon manuell registrering fra tekst</t>

--- a/data/arbeidsfiler/weekly_results_2026.xlsx
+++ b/data/arbeidsfiler/weekly_results_2026.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE376"/>
+  <dimension ref="A1:AE379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26674,10 +26674,8 @@
           <t>15:32</t>
         </is>
       </c>
-      <c r="N257" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="N257" t="n">
+        <v>38</v>
       </c>
       <c r="O257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
@@ -26720,10 +26718,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z257" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
+      <c r="Z257" t="n">
+        <v>27</v>
       </c>
       <c r="AA257" t="inlineStr">
         <is>
@@ -26795,10 +26791,8 @@
           <t>19:28</t>
         </is>
       </c>
-      <c r="N258" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="N258" t="n">
+        <v>42</v>
       </c>
       <c r="O258" t="inlineStr"/>
       <c r="P258" t="inlineStr">
@@ -26841,10 +26835,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z258" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="Z258" t="n">
+        <v>30</v>
       </c>
       <c r="AA258" t="inlineStr">
         <is>
@@ -26916,10 +26908,8 @@
           <t>15:39</t>
         </is>
       </c>
-      <c r="N259" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="N259" t="n">
+        <v>49</v>
       </c>
       <c r="O259" t="inlineStr"/>
       <c r="P259" t="inlineStr">
@@ -26962,10 +26952,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z259" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
+      <c r="Z259" t="n">
+        <v>6</v>
       </c>
       <c r="AA259" t="inlineStr">
         <is>
@@ -27037,10 +27025,8 @@
           <t>15:45</t>
         </is>
       </c>
-      <c r="N260" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="N260" t="n">
+        <v>50</v>
       </c>
       <c r="O260" t="inlineStr"/>
       <c r="P260" t="inlineStr">
@@ -27083,10 +27069,8 @@
           <t>M18-19</t>
         </is>
       </c>
-      <c r="Z260" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="Z260" t="n">
+        <v>4</v>
       </c>
       <c r="AA260" t="inlineStr">
         <is>
@@ -27158,10 +27142,8 @@
           <t>15:32</t>
         </is>
       </c>
-      <c r="N261" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="N261" t="n">
+        <v>61</v>
       </c>
       <c r="O261" t="inlineStr"/>
       <c r="P261" t="inlineStr">
@@ -27204,10 +27186,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
+      <c r="Z261" t="n">
+        <v>42</v>
       </c>
       <c r="AA261" t="inlineStr">
         <is>
@@ -27279,10 +27259,8 @@
           <t>15:50</t>
         </is>
       </c>
-      <c r="N262" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="N262" t="n">
+        <v>86</v>
       </c>
       <c r="O262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
@@ -27325,10 +27303,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
+      <c r="Z262" t="n">
+        <v>11</v>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
@@ -27400,10 +27376,8 @@
           <t>16:06</t>
         </is>
       </c>
-      <c r="N263" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="N263" t="n">
+        <v>92</v>
       </c>
       <c r="O263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
@@ -27446,10 +27420,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
+      <c r="Z263" t="n">
+        <v>59</v>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
@@ -27521,10 +27493,8 @@
           <t>16:05</t>
         </is>
       </c>
-      <c r="N264" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
+      <c r="N264" t="n">
+        <v>107</v>
       </c>
       <c r="O264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
@@ -27567,10 +27537,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
+      <c r="Z264" t="n">
+        <v>9</v>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
@@ -27642,10 +27610,8 @@
           <t>16:14</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="N265" t="n">
+        <v>116</v>
       </c>
       <c r="O265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
@@ -27688,10 +27654,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
+      <c r="Z265" t="n">
+        <v>11</v>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
@@ -27763,10 +27727,8 @@
           <t>16:18</t>
         </is>
       </c>
-      <c r="N266" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="N266" t="n">
+        <v>4</v>
       </c>
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
@@ -27809,10 +27771,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="Z266" t="n">
+        <v>2</v>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
@@ -27884,10 +27844,8 @@
           <t>16:23</t>
         </is>
       </c>
-      <c r="N267" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="N267" t="n">
+        <v>127</v>
       </c>
       <c r="O267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
@@ -27930,10 +27888,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
+      <c r="Z267" t="n">
+        <v>77</v>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
@@ -28005,10 +27961,8 @@
           <t>16:33</t>
         </is>
       </c>
-      <c r="N268" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+      <c r="N268" t="n">
+        <v>133</v>
       </c>
       <c r="O268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
@@ -28051,10 +28005,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
+      <c r="Z268" t="n">
+        <v>81</v>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
@@ -28126,10 +28078,8 @@
           <t>16:33</t>
         </is>
       </c>
-      <c r="N269" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+      <c r="N269" t="n">
+        <v>141</v>
       </c>
       <c r="O269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
@@ -28243,10 +28193,8 @@
           <t>16:22</t>
         </is>
       </c>
-      <c r="N270" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
+      <c r="N270" t="n">
+        <v>142</v>
       </c>
       <c r="O270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
@@ -28289,10 +28237,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
+      <c r="Z270" t="n">
+        <v>27</v>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
@@ -28364,10 +28310,8 @@
           <t>16:20</t>
         </is>
       </c>
-      <c r="N271" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
+      <c r="N271" t="n">
+        <v>144</v>
       </c>
       <c r="O271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
@@ -28410,10 +28354,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
+      <c r="Z271" t="n">
+        <v>85</v>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
@@ -28485,10 +28427,8 @@
           <t>16:28</t>
         </is>
       </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="N272" t="n">
+        <v>149</v>
       </c>
       <c r="O272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
@@ -28531,10 +28471,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
+      <c r="Z272" t="n">
+        <v>87</v>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
@@ -28606,10 +28544,8 @@
           <t>16:42</t>
         </is>
       </c>
-      <c r="N273" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
+      <c r="N273" t="n">
+        <v>179</v>
       </c>
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
@@ -28652,10 +28588,8 @@
           <t>M45-49</t>
         </is>
       </c>
-      <c r="Z273" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
+      <c r="Z273" t="n">
+        <v>6</v>
       </c>
       <c r="AA273" t="inlineStr">
         <is>
@@ -28727,10 +28661,8 @@
           <t>16:34</t>
         </is>
       </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="N274" t="n">
+        <v>200</v>
       </c>
       <c r="O274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
@@ -28773,10 +28705,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
+      <c r="Z274" t="n">
+        <v>118</v>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
@@ -28848,10 +28778,8 @@
           <t>16:40</t>
         </is>
       </c>
-      <c r="N275" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
+      <c r="N275" t="n">
+        <v>212</v>
       </c>
       <c r="O275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
@@ -28965,10 +28893,8 @@
           <t>16:44</t>
         </is>
       </c>
-      <c r="N276" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
+      <c r="N276" t="n">
+        <v>201</v>
       </c>
       <c r="O276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
@@ -29011,10 +28937,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>119.0</t>
-        </is>
+      <c r="Z276" t="n">
+        <v>119</v>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
@@ -29086,10 +29010,8 @@
           <t>17:06</t>
         </is>
       </c>
-      <c r="N277" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
+      <c r="N277" t="n">
+        <v>213</v>
       </c>
       <c r="O277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
@@ -29132,10 +29054,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
+      <c r="Z277" t="n">
+        <v>128</v>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
@@ -29207,10 +29127,8 @@
           <t>17:06</t>
         </is>
       </c>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+      <c r="N278" t="n">
+        <v>220</v>
       </c>
       <c r="O278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
@@ -29253,10 +29171,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z278" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
+      <c r="Z278" t="n">
+        <v>130</v>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
@@ -29328,10 +29244,8 @@
           <t>16:08</t>
         </is>
       </c>
-      <c r="N279" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
+      <c r="N279" t="n">
+        <v>238</v>
       </c>
       <c r="O279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
@@ -29445,10 +29359,8 @@
           <t>17:08</t>
         </is>
       </c>
-      <c r="N280" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
+      <c r="N280" t="n">
+        <v>227</v>
       </c>
       <c r="O280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
@@ -29491,10 +29403,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z280" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
+      <c r="Z280" t="n">
+        <v>21</v>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
@@ -29566,10 +29476,8 @@
           <t>16:55</t>
         </is>
       </c>
-      <c r="N281" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
+      <c r="N281" t="n">
+        <v>228</v>
       </c>
       <c r="O281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
@@ -29612,10 +29520,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z281" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
+      <c r="Z281" t="n">
+        <v>45</v>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
@@ -29687,10 +29593,8 @@
           <t>17:06</t>
         </is>
       </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
+      <c r="N282" t="n">
+        <v>251</v>
       </c>
       <c r="O282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
@@ -29733,10 +29637,8 @@
           <t>M45-49</t>
         </is>
       </c>
-      <c r="Z282" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
+      <c r="Z282" t="n">
+        <v>10</v>
       </c>
       <c r="AA282" t="inlineStr">
         <is>
@@ -29808,10 +29710,8 @@
           <t>17:07</t>
         </is>
       </c>
-      <c r="N283" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
+      <c r="N283" t="n">
+        <v>258</v>
       </c>
       <c r="O283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
@@ -29854,10 +29754,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z283" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
+      <c r="Z283" t="n">
+        <v>25</v>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
@@ -29929,10 +29827,8 @@
           <t>17:18</t>
         </is>
       </c>
-      <c r="N284" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
+      <c r="N284" t="n">
+        <v>261</v>
       </c>
       <c r="O284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
@@ -29975,10 +29871,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z284" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
+      <c r="Z284" t="n">
+        <v>149</v>
       </c>
       <c r="AA284" t="inlineStr">
         <is>
@@ -30050,10 +29944,8 @@
           <t>17:08</t>
         </is>
       </c>
-      <c r="N285" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+      <c r="N285" t="n">
+        <v>269</v>
       </c>
       <c r="O285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
@@ -30096,10 +29988,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z285" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
+      <c r="Z285" t="n">
+        <v>58</v>
       </c>
       <c r="AA285" t="inlineStr">
         <is>
@@ -30171,10 +30061,8 @@
           <t>16:55</t>
         </is>
       </c>
-      <c r="N286" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="N286" t="n">
+        <v>270</v>
       </c>
       <c r="O286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
@@ -30217,10 +30105,8 @@
           <t>M45-49</t>
         </is>
       </c>
-      <c r="Z286" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
+      <c r="Z286" t="n">
+        <v>11</v>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
@@ -30292,10 +30178,8 @@
           <t>17:04</t>
         </is>
       </c>
-      <c r="N287" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
+      <c r="N287" t="n">
+        <v>277</v>
       </c>
       <c r="O287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
@@ -30338,10 +30222,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z287" t="inlineStr">
-        <is>
-          <t>157.0</t>
-        </is>
+      <c r="Z287" t="n">
+        <v>157</v>
       </c>
       <c r="AA287" t="inlineStr">
         <is>
@@ -30413,10 +30295,8 @@
           <t>16:55</t>
         </is>
       </c>
-      <c r="N288" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="N288" t="n">
+        <v>14</v>
       </c>
       <c r="O288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
@@ -30459,10 +30339,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z288" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
+      <c r="Z288" t="n">
+        <v>10</v>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
@@ -30534,10 +30412,8 @@
           <t>17:20</t>
         </is>
       </c>
-      <c r="N289" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
+      <c r="N289" t="n">
+        <v>294</v>
       </c>
       <c r="O289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
@@ -30580,10 +30456,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z289" t="inlineStr">
-        <is>
-          <t>168.0</t>
-        </is>
+      <c r="Z289" t="n">
+        <v>168</v>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
@@ -30655,10 +30529,8 @@
           <t>17:19</t>
         </is>
       </c>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="N290" t="n">
+        <v>17</v>
       </c>
       <c r="O290" t="inlineStr"/>
       <c r="P290" t="inlineStr">
@@ -30701,10 +30573,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z290" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
+      <c r="Z290" t="n">
+        <v>11</v>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
@@ -30776,10 +30646,8 @@
           <t>17:22</t>
         </is>
       </c>
-      <c r="N291" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="N291" t="n">
+        <v>18</v>
       </c>
       <c r="O291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
@@ -30822,10 +30690,8 @@
           <t>K35-39</t>
         </is>
       </c>
-      <c r="Z291" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="Z291" t="n">
+        <v>3</v>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
@@ -30897,10 +30763,8 @@
           <t>17:03</t>
         </is>
       </c>
-      <c r="N292" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
+      <c r="N292" t="n">
+        <v>320</v>
       </c>
       <c r="O292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
@@ -30943,10 +30807,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z292" t="inlineStr">
-        <is>
-          <t>184.0</t>
-        </is>
+      <c r="Z292" t="n">
+        <v>184</v>
       </c>
       <c r="AA292" t="inlineStr">
         <is>
@@ -31018,10 +30880,8 @@
           <t>16:37</t>
         </is>
       </c>
-      <c r="N293" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="N293" t="n">
+        <v>20</v>
       </c>
       <c r="O293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
@@ -31064,10 +30924,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z293" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
+      <c r="Z293" t="n">
+        <v>13</v>
       </c>
       <c r="AA293" t="inlineStr">
         <is>
@@ -31139,10 +30997,8 @@
           <t>17:04</t>
         </is>
       </c>
-      <c r="N294" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
+      <c r="N294" t="n">
+        <v>331</v>
       </c>
       <c r="O294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
@@ -31185,10 +31041,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z294" t="inlineStr">
-        <is>
-          <t>191.0</t>
-        </is>
+      <c r="Z294" t="n">
+        <v>191</v>
       </c>
       <c r="AA294" t="inlineStr">
         <is>
@@ -31260,10 +31114,8 @@
           <t>17:15</t>
         </is>
       </c>
-      <c r="N295" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
+      <c r="N295" t="n">
+        <v>339</v>
       </c>
       <c r="O295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
@@ -31306,10 +31158,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z295" t="inlineStr">
-        <is>
-          <t>196.0</t>
-        </is>
+      <c r="Z295" t="n">
+        <v>196</v>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
@@ -31381,10 +31231,8 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="N296" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
+      <c r="N296" t="n">
+        <v>345</v>
       </c>
       <c r="O296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
@@ -31427,10 +31275,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z296" t="inlineStr">
-        <is>
-          <t>201.0</t>
-        </is>
+      <c r="Z296" t="n">
+        <v>201</v>
       </c>
       <c r="AA296" t="inlineStr">
         <is>
@@ -31502,10 +31348,8 @@
           <t>17:22</t>
         </is>
       </c>
-      <c r="N297" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="N297" t="n">
+        <v>23</v>
       </c>
       <c r="O297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
@@ -31548,10 +31392,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z297" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
+      <c r="Z297" t="n">
+        <v>14</v>
       </c>
       <c r="AA297" t="inlineStr">
         <is>
@@ -31623,10 +31465,8 @@
           <t>17:22</t>
         </is>
       </c>
-      <c r="N298" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="N298" t="n">
+        <v>24</v>
       </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="inlineStr">
@@ -31669,10 +31509,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z298" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
+      <c r="Z298" t="n">
+        <v>15</v>
       </c>
       <c r="AA298" t="inlineStr">
         <is>
@@ -31744,10 +31582,8 @@
           <t>17:43</t>
         </is>
       </c>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
+      <c r="N299" t="n">
+        <v>405</v>
       </c>
       <c r="O299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
@@ -31790,10 +31626,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z299" t="inlineStr">
-        <is>
-          <t>230.0</t>
-        </is>
+      <c r="Z299" t="n">
+        <v>230</v>
       </c>
       <c r="AA299" t="inlineStr">
         <is>
@@ -31865,10 +31699,8 @@
           <t>17:40</t>
         </is>
       </c>
-      <c r="N300" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
+      <c r="N300" t="n">
+        <v>411</v>
       </c>
       <c r="O300" t="inlineStr"/>
       <c r="P300" t="inlineStr">
@@ -31911,10 +31743,8 @@
           <t>M18-19</t>
         </is>
       </c>
-      <c r="Z300" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
+      <c r="Z300" t="n">
+        <v>10</v>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
@@ -31986,10 +31816,8 @@
           <t>17:43</t>
         </is>
       </c>
-      <c r="N301" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
+      <c r="N301" t="n">
+        <v>418</v>
       </c>
       <c r="O301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
@@ -32032,10 +31860,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z301" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
+      <c r="Z301" t="n">
+        <v>92</v>
       </c>
       <c r="AA301" t="inlineStr">
         <is>
@@ -32107,10 +31933,8 @@
           <t>17:18</t>
         </is>
       </c>
-      <c r="N302" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
+      <c r="N302" t="n">
+        <v>422</v>
       </c>
       <c r="O302" t="inlineStr"/>
       <c r="P302" t="inlineStr">
@@ -32153,10 +31977,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z302" t="inlineStr">
-        <is>
-          <t>242.0</t>
-        </is>
+      <c r="Z302" t="n">
+        <v>242</v>
       </c>
       <c r="AA302" t="inlineStr">
         <is>
@@ -32228,10 +32050,8 @@
           <t>18:18</t>
         </is>
       </c>
-      <c r="N303" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
+      <c r="N303" t="n">
+        <v>471</v>
       </c>
       <c r="O303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
@@ -32274,10 +32094,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z303" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
+      <c r="Z303" t="n">
+        <v>102</v>
       </c>
       <c r="AA303" t="inlineStr">
         <is>
@@ -32349,10 +32167,8 @@
           <t>17:58</t>
         </is>
       </c>
-      <c r="N304" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="N304" t="n">
+        <v>32</v>
       </c>
       <c r="O304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
@@ -32395,10 +32211,8 @@
           <t>K20-22</t>
         </is>
       </c>
-      <c r="Z304" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
+      <c r="Z304" t="n">
+        <v>7</v>
       </c>
       <c r="AA304" t="inlineStr">
         <is>
@@ -32470,10 +32284,8 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="N305" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
+      <c r="N305" t="n">
+        <v>506</v>
       </c>
       <c r="O305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
@@ -32516,10 +32328,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z305" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
+      <c r="Z305" t="n">
+        <v>110</v>
       </c>
       <c r="AA305" t="inlineStr">
         <is>
@@ -32591,10 +32401,8 @@
           <t>17:46</t>
         </is>
       </c>
-      <c r="N306" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
+      <c r="N306" t="n">
+        <v>523</v>
       </c>
       <c r="O306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
@@ -32637,10 +32445,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z306" t="inlineStr">
-        <is>
-          <t>298.0</t>
-        </is>
+      <c r="Z306" t="n">
+        <v>298</v>
       </c>
       <c r="AA306" t="inlineStr">
         <is>
@@ -32712,10 +32518,8 @@
           <t>18:13</t>
         </is>
       </c>
-      <c r="N307" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
+      <c r="N307" t="n">
+        <v>604</v>
       </c>
       <c r="O307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
@@ -32758,10 +32562,8 @@
           <t>M55-59</t>
         </is>
       </c>
-      <c r="Z307" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="Z307" t="n">
+        <v>5</v>
       </c>
       <c r="AA307" t="inlineStr">
         <is>
@@ -32833,10 +32635,8 @@
           <t>18:25</t>
         </is>
       </c>
-      <c r="N308" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
+      <c r="N308" t="n">
+        <v>630</v>
       </c>
       <c r="O308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
@@ -32879,10 +32679,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z308" t="inlineStr">
-        <is>
-          <t>349.0</t>
-        </is>
+      <c r="Z308" t="n">
+        <v>349</v>
       </c>
       <c r="AA308" t="inlineStr">
         <is>
@@ -32954,10 +32752,8 @@
           <t>18:21</t>
         </is>
       </c>
-      <c r="N309" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
+      <c r="N309" t="n">
+        <v>640</v>
       </c>
       <c r="O309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
@@ -33000,10 +32796,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z309" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
+      <c r="Z309" t="n">
+        <v>143</v>
       </c>
       <c r="AA309" t="inlineStr">
         <is>
@@ -33075,10 +32869,8 @@
           <t>18:33</t>
         </is>
       </c>
-      <c r="N310" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
+      <c r="N310" t="n">
+        <v>688</v>
       </c>
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
@@ -33121,10 +32913,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z310" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
+      <c r="Z310" t="n">
+        <v>155</v>
       </c>
       <c r="AA310" t="inlineStr">
         <is>
@@ -33196,10 +32986,8 @@
           <t>18:35</t>
         </is>
       </c>
-      <c r="N311" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
+      <c r="N311" t="n">
+        <v>691</v>
       </c>
       <c r="O311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
@@ -33242,10 +33030,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z311" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
+      <c r="Z311" t="n">
+        <v>66</v>
       </c>
       <c r="AA311" t="inlineStr">
         <is>
@@ -33317,10 +33103,8 @@
           <t>18:33</t>
         </is>
       </c>
-      <c r="N312" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
+      <c r="N312" t="n">
+        <v>693</v>
       </c>
       <c r="O312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
@@ -33363,10 +33147,8 @@
           <t>M60-64</t>
         </is>
       </c>
-      <c r="Z312" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="Z312" t="n">
+        <v>1</v>
       </c>
       <c r="AA312" t="inlineStr">
         <is>
@@ -33438,10 +33220,8 @@
           <t>18:40</t>
         </is>
       </c>
-      <c r="N313" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="N313" t="n">
+        <v>46</v>
       </c>
       <c r="O313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
@@ -33484,10 +33264,8 @@
           <t>K35-39</t>
         </is>
       </c>
-      <c r="Z313" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
+      <c r="Z313" t="n">
+        <v>11</v>
       </c>
       <c r="AA313" t="inlineStr">
         <is>
@@ -33559,10 +33337,8 @@
           <t>18:38</t>
         </is>
       </c>
-      <c r="N314" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
+      <c r="N314" t="n">
+        <v>768</v>
       </c>
       <c r="O314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
@@ -33605,10 +33381,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z314" t="inlineStr">
-        <is>
-          <t>416.0</t>
-        </is>
+      <c r="Z314" t="n">
+        <v>416</v>
       </c>
       <c r="AA314" t="inlineStr">
         <is>
@@ -33680,10 +33454,8 @@
           <t>18:48</t>
         </is>
       </c>
-      <c r="N315" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
+      <c r="N315" t="n">
+        <v>769</v>
       </c>
       <c r="O315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
@@ -33726,10 +33498,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z315" t="inlineStr">
-        <is>
-          <t>417.0</t>
-        </is>
+      <c r="Z315" t="n">
+        <v>417</v>
       </c>
       <c r="AA315" t="inlineStr">
         <is>
@@ -33801,10 +33571,8 @@
           <t>19:05</t>
         </is>
       </c>
-      <c r="N316" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="N316" t="n">
+        <v>800</v>
       </c>
       <c r="O316" t="inlineStr"/>
       <c r="P316" t="inlineStr">
@@ -33847,10 +33615,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z316" t="inlineStr">
-        <is>
-          <t>430.0</t>
-        </is>
+      <c r="Z316" t="n">
+        <v>430</v>
       </c>
       <c r="AA316" t="inlineStr">
         <is>
@@ -33922,10 +33688,8 @@
           <t>19:02</t>
         </is>
       </c>
-      <c r="N317" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
+      <c r="N317" t="n">
+        <v>818</v>
       </c>
       <c r="O317" t="inlineStr"/>
       <c r="P317" t="inlineStr">
@@ -33968,10 +33732,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z317" t="inlineStr">
-        <is>
-          <t>441.0</t>
-        </is>
+      <c r="Z317" t="n">
+        <v>441</v>
       </c>
       <c r="AA317" t="inlineStr">
         <is>
@@ -34043,10 +33805,8 @@
           <t>18:52</t>
         </is>
       </c>
-      <c r="N318" t="inlineStr">
-        <is>
-          <t>820</t>
-        </is>
+      <c r="N318" t="n">
+        <v>820</v>
       </c>
       <c r="O318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
@@ -34089,10 +33849,8 @@
           <t>M60-64</t>
         </is>
       </c>
-      <c r="Z318" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="Z318" t="n">
+        <v>3</v>
       </c>
       <c r="AA318" t="inlineStr">
         <is>
@@ -34164,10 +33922,8 @@
           <t>18:34</t>
         </is>
       </c>
-      <c r="N319" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
+      <c r="N319" t="n">
+        <v>825</v>
       </c>
       <c r="O319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
@@ -34210,10 +33966,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z319" t="inlineStr">
-        <is>
-          <t>187.0</t>
-        </is>
+      <c r="Z319" t="n">
+        <v>187</v>
       </c>
       <c r="AA319" t="inlineStr">
         <is>
@@ -34285,10 +34039,8 @@
           <t>18:53</t>
         </is>
       </c>
-      <c r="N320" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
+      <c r="N320" t="n">
+        <v>871</v>
       </c>
       <c r="O320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
@@ -34331,10 +34083,8 @@
           <t>M60-64</t>
         </is>
       </c>
-      <c r="Z320" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="Z320" t="n">
+        <v>4</v>
       </c>
       <c r="AA320" t="inlineStr">
         <is>
@@ -34406,10 +34156,8 @@
           <t>18:37</t>
         </is>
       </c>
-      <c r="N321" t="inlineStr">
-        <is>
-          <t>954</t>
-        </is>
+      <c r="N321" t="n">
+        <v>954</v>
       </c>
       <c r="O321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
@@ -34523,10 +34271,8 @@
           <t>19:04</t>
         </is>
       </c>
-      <c r="N322" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
+      <c r="N322" t="n">
+        <v>903</v>
       </c>
       <c r="O322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
@@ -34569,10 +34315,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z322" t="inlineStr">
-        <is>
-          <t>492.0</t>
-        </is>
+      <c r="Z322" t="n">
+        <v>492</v>
       </c>
       <c r="AA322" t="inlineStr">
         <is>
@@ -34644,10 +34388,8 @@
           <t>19:10</t>
         </is>
       </c>
-      <c r="N323" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="N323" t="n">
+        <v>66</v>
       </c>
       <c r="O323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
@@ -34690,10 +34432,8 @@
           <t>K45-49</t>
         </is>
       </c>
-      <c r="Z323" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="Z323" t="n">
+        <v>1</v>
       </c>
       <c r="AA323" t="inlineStr">
         <is>
@@ -34765,10 +34505,8 @@
           <t>19:11</t>
         </is>
       </c>
-      <c r="N324" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="N324" t="n">
+        <v>67</v>
       </c>
       <c r="O324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
@@ -34811,10 +34549,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z324" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
+      <c r="Z324" t="n">
+        <v>38</v>
       </c>
       <c r="AA324" t="inlineStr">
         <is>
@@ -34886,10 +34622,8 @@
           <t>18:53</t>
         </is>
       </c>
-      <c r="N325" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="N325" t="n">
+        <v>74</v>
       </c>
       <c r="O325" t="inlineStr"/>
       <c r="P325" t="inlineStr">
@@ -34932,10 +34666,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z325" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
+      <c r="Z325" t="n">
+        <v>43</v>
       </c>
       <c r="AA325" t="inlineStr">
         <is>
@@ -35007,10 +34739,8 @@
           <t>19:08</t>
         </is>
       </c>
-      <c r="N326" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
+      <c r="N326" t="n">
+        <v>968</v>
       </c>
       <c r="O326" t="inlineStr"/>
       <c r="P326" t="inlineStr">
@@ -35053,10 +34783,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z326" t="inlineStr">
-        <is>
-          <t>524.0</t>
-        </is>
+      <c r="Z326" t="n">
+        <v>524</v>
       </c>
       <c r="AA326" t="inlineStr">
         <is>
@@ -35128,10 +34856,8 @@
           <t>18:58</t>
         </is>
       </c>
-      <c r="N327" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="N327" t="n">
+        <v>81</v>
       </c>
       <c r="O327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
@@ -35174,10 +34900,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z327" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
+      <c r="Z327" t="n">
+        <v>46</v>
       </c>
       <c r="AA327" t="inlineStr">
         <is>
@@ -35249,10 +34973,8 @@
           <t>19:09</t>
         </is>
       </c>
-      <c r="N328" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="N328" t="n">
+        <v>84</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
@@ -35295,10 +35017,8 @@
           <t>K35-39</t>
         </is>
       </c>
-      <c r="Z328" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
+      <c r="Z328" t="n">
+        <v>20</v>
       </c>
       <c r="AA328" t="inlineStr">
         <is>
@@ -35370,10 +35090,8 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>1078</t>
-        </is>
+      <c r="N329" t="n">
+        <v>1078</v>
       </c>
       <c r="O329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
@@ -35416,10 +35134,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z329" t="inlineStr">
-        <is>
-          <t>569.0</t>
-        </is>
+      <c r="Z329" t="n">
+        <v>569</v>
       </c>
       <c r="AA329" t="inlineStr">
         <is>
@@ -35491,10 +35207,8 @@
           <t>19:45</t>
         </is>
       </c>
-      <c r="N330" t="inlineStr">
-        <is>
-          <t>1098</t>
-        </is>
+      <c r="N330" t="n">
+        <v>1098</v>
       </c>
       <c r="O330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
@@ -35537,10 +35251,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z330" t="inlineStr">
-        <is>
-          <t>238.0</t>
-        </is>
+      <c r="Z330" t="n">
+        <v>238</v>
       </c>
       <c r="AA330" t="inlineStr">
         <is>
@@ -35612,10 +35324,8 @@
           <t>18:51</t>
         </is>
       </c>
-      <c r="N331" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
+      <c r="N331" t="n">
+        <v>1122</v>
       </c>
       <c r="O331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
@@ -35658,10 +35368,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z331" t="inlineStr">
-        <is>
-          <t>582.0</t>
-        </is>
+      <c r="Z331" t="n">
+        <v>582</v>
       </c>
       <c r="AA331" t="inlineStr">
         <is>
@@ -35733,10 +35441,8 @@
           <t>19:36</t>
         </is>
       </c>
-      <c r="N332" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+      <c r="N332" t="n">
+        <v>93</v>
       </c>
       <c r="O332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
@@ -35779,10 +35485,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z332" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
+      <c r="Z332" t="n">
+        <v>53</v>
       </c>
       <c r="AA332" t="inlineStr">
         <is>
@@ -35854,10 +35558,8 @@
           <t>19:51</t>
         </is>
       </c>
-      <c r="N333" t="inlineStr">
-        <is>
-          <t>1137</t>
-        </is>
+      <c r="N333" t="n">
+        <v>1137</v>
       </c>
       <c r="O333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
@@ -35900,10 +35602,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z333" t="inlineStr">
-        <is>
-          <t>252.0</t>
-        </is>
+      <c r="Z333" t="n">
+        <v>252</v>
       </c>
       <c r="AA333" t="inlineStr">
         <is>
@@ -35975,10 +35675,8 @@
           <t>19:45</t>
         </is>
       </c>
-      <c r="N334" t="inlineStr">
-        <is>
-          <t>1148</t>
-        </is>
+      <c r="N334" t="n">
+        <v>1148</v>
       </c>
       <c r="O334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
@@ -36021,10 +35719,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z334" t="inlineStr">
-        <is>
-          <t>596.0</t>
-        </is>
+      <c r="Z334" t="n">
+        <v>596</v>
       </c>
       <c r="AA334" t="inlineStr">
         <is>
@@ -36096,10 +35792,8 @@
           <t>19:50</t>
         </is>
       </c>
-      <c r="N335" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+      <c r="N335" t="n">
+        <v>105</v>
       </c>
       <c r="O335" t="inlineStr"/>
       <c r="P335" t="inlineStr">
@@ -36142,10 +35836,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z335" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
+      <c r="Z335" t="n">
+        <v>61</v>
       </c>
       <c r="AA335" t="inlineStr">
         <is>
@@ -36217,10 +35909,8 @@
           <t>19:43</t>
         </is>
       </c>
-      <c r="N336" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="N336" t="n">
+        <v>110</v>
       </c>
       <c r="O336" t="inlineStr"/>
       <c r="P336" t="inlineStr">
@@ -36263,10 +35953,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z336" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
+      <c r="Z336" t="n">
+        <v>64</v>
       </c>
       <c r="AA336" t="inlineStr">
         <is>
@@ -36338,10 +36026,8 @@
           <t>19:50</t>
         </is>
       </c>
-      <c r="N337" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
+      <c r="N337" t="n">
+        <v>1217</v>
       </c>
       <c r="O337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
@@ -36384,10 +36070,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z337" t="inlineStr">
-        <is>
-          <t>626.0</t>
-        </is>
+      <c r="Z337" t="n">
+        <v>626</v>
       </c>
       <c r="AA337" t="inlineStr">
         <is>
@@ -36459,10 +36143,8 @@
           <t>19:38</t>
         </is>
       </c>
-      <c r="N338" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
+      <c r="N338" t="n">
+        <v>1224</v>
       </c>
       <c r="O338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
@@ -36505,10 +36187,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z338" t="inlineStr">
-        <is>
-          <t>628.0</t>
-        </is>
+      <c r="Z338" t="n">
+        <v>628</v>
       </c>
       <c r="AA338" t="inlineStr">
         <is>
@@ -36580,10 +36260,8 @@
           <t>19:37</t>
         </is>
       </c>
-      <c r="N339" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
+      <c r="N339" t="n">
+        <v>1236</v>
       </c>
       <c r="O339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
@@ -36626,10 +36304,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z339" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
+      <c r="Z339" t="n">
+        <v>144</v>
       </c>
       <c r="AA339" t="inlineStr">
         <is>
@@ -36701,10 +36377,8 @@
           <t>19:21</t>
         </is>
       </c>
-      <c r="N340" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="N340" t="n">
+        <v>124</v>
       </c>
       <c r="O340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
@@ -36747,10 +36421,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z340" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
+      <c r="Z340" t="n">
+        <v>72</v>
       </c>
       <c r="AA340" t="inlineStr">
         <is>
@@ -36822,10 +36494,8 @@
           <t>17:32</t>
         </is>
       </c>
-      <c r="N341" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
+      <c r="N341" t="n">
+        <v>1261</v>
       </c>
       <c r="O341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
@@ -36868,10 +36538,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z341" t="inlineStr">
-        <is>
-          <t>288.0</t>
-        </is>
+      <c r="Z341" t="n">
+        <v>288</v>
       </c>
       <c r="AA341" t="inlineStr">
         <is>
@@ -36943,10 +36611,8 @@
           <t>19:26</t>
         </is>
       </c>
-      <c r="N342" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
+      <c r="N342" t="n">
+        <v>1305</v>
       </c>
       <c r="O342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
@@ -36989,10 +36655,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z342" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
+      <c r="Z342" t="n">
+        <v>300</v>
       </c>
       <c r="AA342" t="inlineStr">
         <is>
@@ -37064,10 +36728,8 @@
           <t>20:02</t>
         </is>
       </c>
-      <c r="N343" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
+      <c r="N343" t="n">
+        <v>132</v>
       </c>
       <c r="O343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
@@ -37110,10 +36772,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z343" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
+      <c r="Z343" t="n">
+        <v>79</v>
       </c>
       <c r="AA343" t="inlineStr">
         <is>
@@ -37185,10 +36845,8 @@
           <t>19:48</t>
         </is>
       </c>
-      <c r="N344" t="inlineStr">
-        <is>
-          <t>1362</t>
-        </is>
+      <c r="N344" t="n">
+        <v>1362</v>
       </c>
       <c r="O344" t="inlineStr"/>
       <c r="P344" t="inlineStr">
@@ -37231,10 +36889,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z344" t="inlineStr">
-        <is>
-          <t>688.0</t>
-        </is>
+      <c r="Z344" t="n">
+        <v>688</v>
       </c>
       <c r="AA344" t="inlineStr">
         <is>
@@ -37306,10 +36962,8 @@
           <t>19:50</t>
         </is>
       </c>
-      <c r="N345" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="N345" t="n">
+        <v>138</v>
       </c>
       <c r="O345" t="inlineStr"/>
       <c r="P345" t="inlineStr">
@@ -37352,10 +37006,8 @@
           <t>K20-22</t>
         </is>
       </c>
-      <c r="Z345" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
+      <c r="Z345" t="n">
+        <v>12</v>
       </c>
       <c r="AA345" t="inlineStr">
         <is>
@@ -37427,10 +37079,8 @@
           <t>20:01</t>
         </is>
       </c>
-      <c r="N346" t="inlineStr">
-        <is>
-          <t>1395</t>
-        </is>
+      <c r="N346" t="n">
+        <v>1395</v>
       </c>
       <c r="O346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
@@ -37473,10 +37123,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z346" t="inlineStr">
-        <is>
-          <t>169.0</t>
-        </is>
+      <c r="Z346" t="n">
+        <v>169</v>
       </c>
       <c r="AA346" t="inlineStr">
         <is>
@@ -37548,10 +37196,8 @@
           <t>19:57</t>
         </is>
       </c>
-      <c r="N347" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
+      <c r="N347" t="n">
+        <v>144</v>
       </c>
       <c r="O347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
@@ -37594,10 +37240,8 @@
           <t>K35-39</t>
         </is>
       </c>
-      <c r="Z347" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
+      <c r="Z347" t="n">
+        <v>28</v>
       </c>
       <c r="AA347" t="inlineStr">
         <is>
@@ -37669,10 +37313,8 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="N348" t="inlineStr">
-        <is>
-          <t>1407</t>
-        </is>
+      <c r="N348" t="n">
+        <v>1407</v>
       </c>
       <c r="O348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
@@ -37715,10 +37357,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z348" t="inlineStr">
-        <is>
-          <t>705.0</t>
-        </is>
+      <c r="Z348" t="n">
+        <v>705</v>
       </c>
       <c r="AA348" t="inlineStr">
         <is>
@@ -37790,10 +37430,8 @@
           <t>20:11</t>
         </is>
       </c>
-      <c r="N349" t="inlineStr">
-        <is>
-          <t>1432</t>
-        </is>
+      <c r="N349" t="n">
+        <v>1432</v>
       </c>
       <c r="O349" t="inlineStr"/>
       <c r="P349" t="inlineStr">
@@ -37836,10 +37474,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z349" t="inlineStr">
-        <is>
-          <t>722.0</t>
-        </is>
+      <c r="Z349" t="n">
+        <v>722</v>
       </c>
       <c r="AA349" t="inlineStr">
         <is>
@@ -37911,10 +37547,8 @@
           <t>20:01</t>
         </is>
       </c>
-      <c r="N350" t="inlineStr">
-        <is>
-          <t>1515</t>
-        </is>
+      <c r="N350" t="n">
+        <v>1515</v>
       </c>
       <c r="O350" t="inlineStr"/>
       <c r="P350" t="inlineStr">
@@ -37957,10 +37591,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z350" t="inlineStr">
-        <is>
-          <t>760.0</t>
-        </is>
+      <c r="Z350" t="n">
+        <v>760</v>
       </c>
       <c r="AA350" t="inlineStr">
         <is>
@@ -38032,10 +37664,8 @@
           <t>20:31</t>
         </is>
       </c>
-      <c r="N351" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
+      <c r="N351" t="n">
+        <v>175</v>
       </c>
       <c r="O351" t="inlineStr"/>
       <c r="P351" t="inlineStr">
@@ -38078,10 +37708,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z351" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
+      <c r="Z351" t="n">
+        <v>97</v>
       </c>
       <c r="AA351" t="inlineStr">
         <is>
@@ -38153,10 +37781,8 @@
           <t>20:11</t>
         </is>
       </c>
-      <c r="N352" t="inlineStr">
-        <is>
-          <t>1659</t>
-        </is>
+      <c r="N352" t="n">
+        <v>1659</v>
       </c>
       <c r="O352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
@@ -38199,10 +37825,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z352" t="inlineStr">
-        <is>
-          <t>816.0</t>
-        </is>
+      <c r="Z352" t="n">
+        <v>816</v>
       </c>
       <c r="AA352" t="inlineStr">
         <is>
@@ -38274,10 +37898,8 @@
           <t>20:38</t>
         </is>
       </c>
-      <c r="N353" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="N353" t="n">
+        <v>192</v>
       </c>
       <c r="O353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
@@ -38320,10 +37942,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z353" t="inlineStr">
-        <is>
-          <t>111.0</t>
-        </is>
+      <c r="Z353" t="n">
+        <v>111</v>
       </c>
       <c r="AA353" t="inlineStr">
         <is>
@@ -38395,10 +38015,8 @@
           <t>20:44</t>
         </is>
       </c>
-      <c r="N354" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
+      <c r="N354" t="n">
+        <v>194</v>
       </c>
       <c r="O354" t="inlineStr"/>
       <c r="P354" t="inlineStr">
@@ -38441,10 +38059,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z354" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
+      <c r="Z354" t="n">
+        <v>112</v>
       </c>
       <c r="AA354" t="inlineStr">
         <is>
@@ -38516,10 +38132,8 @@
           <t>20:51</t>
         </is>
       </c>
-      <c r="N355" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
+      <c r="N355" t="n">
+        <v>203</v>
       </c>
       <c r="O355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
@@ -38562,10 +38176,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z355" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
+      <c r="Z355" t="n">
+        <v>120</v>
       </c>
       <c r="AA355" t="inlineStr">
         <is>
@@ -38637,10 +38249,8 @@
           <t>20:58</t>
         </is>
       </c>
-      <c r="N356" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
+      <c r="N356" t="n">
+        <v>210</v>
       </c>
       <c r="O356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
@@ -38683,10 +38293,8 @@
           <t>K35-39</t>
         </is>
       </c>
-      <c r="Z356" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="Z356" t="n">
+        <v>40</v>
       </c>
       <c r="AA356" t="inlineStr">
         <is>
@@ -38758,10 +38366,8 @@
           <t>20:34</t>
         </is>
       </c>
-      <c r="N357" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
+      <c r="N357" t="n">
+        <v>228</v>
       </c>
       <c r="O357" t="inlineStr"/>
       <c r="P357" t="inlineStr">
@@ -38804,10 +38410,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z357" t="inlineStr">
-        <is>
-          <t>136.0</t>
-        </is>
+      <c r="Z357" t="n">
+        <v>136</v>
       </c>
       <c r="AA357" t="inlineStr">
         <is>
@@ -38879,10 +38483,8 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="N358" t="inlineStr">
-        <is>
-          <t>1787</t>
-        </is>
+      <c r="N358" t="n">
+        <v>1787</v>
       </c>
       <c r="O358" t="inlineStr"/>
       <c r="P358" t="inlineStr">
@@ -38925,10 +38527,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z358" t="inlineStr">
-        <is>
-          <t>873.0</t>
-        </is>
+      <c r="Z358" t="n">
+        <v>873</v>
       </c>
       <c r="AA358" t="inlineStr">
         <is>
@@ -39000,10 +38600,8 @@
           <t>20:54</t>
         </is>
       </c>
-      <c r="N359" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
+      <c r="N359" t="n">
+        <v>238</v>
       </c>
       <c r="O359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
@@ -39046,10 +38644,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z359" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
+      <c r="Z359" t="n">
+        <v>143</v>
       </c>
       <c r="AA359" t="inlineStr">
         <is>
@@ -39121,10 +38717,8 @@
           <t>20:26</t>
         </is>
       </c>
-      <c r="N360" t="inlineStr">
-        <is>
-          <t>1817</t>
-        </is>
+      <c r="N360" t="n">
+        <v>1817</v>
       </c>
       <c r="O360" t="inlineStr"/>
       <c r="P360" t="inlineStr">
@@ -39167,10 +38761,8 @@
           <t>M50-54</t>
         </is>
       </c>
-      <c r="Z360" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+      <c r="Z360" t="n">
+        <v>52</v>
       </c>
       <c r="AA360" t="inlineStr">
         <is>
@@ -39242,10 +38834,8 @@
           <t>21:03</t>
         </is>
       </c>
-      <c r="N361" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="N361" t="n">
+        <v>1826</v>
       </c>
       <c r="O361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
@@ -39288,10 +38878,8 @@
           <t>M55-59</t>
         </is>
       </c>
-      <c r="Z361" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
+      <c r="Z361" t="n">
+        <v>33</v>
       </c>
       <c r="AA361" t="inlineStr">
         <is>
@@ -39363,10 +38951,8 @@
           <t>20:37</t>
         </is>
       </c>
-      <c r="N362" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
+      <c r="N362" t="n">
+        <v>262</v>
       </c>
       <c r="O362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
@@ -39409,10 +38995,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z362" t="inlineStr">
-        <is>
-          <t>157.0</t>
-        </is>
+      <c r="Z362" t="n">
+        <v>157</v>
       </c>
       <c r="AA362" t="inlineStr">
         <is>
@@ -39484,10 +39068,8 @@
           <t>21:07</t>
         </is>
       </c>
-      <c r="N363" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
+      <c r="N363" t="n">
+        <v>264</v>
       </c>
       <c r="O363" t="inlineStr"/>
       <c r="P363" t="inlineStr">
@@ -39530,10 +39112,8 @@
           <t>K18-19</t>
         </is>
       </c>
-      <c r="Z363" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="Z363" t="n">
+        <v>5</v>
       </c>
       <c r="AA363" t="inlineStr">
         <is>
@@ -39605,10 +39185,8 @@
           <t>21:17</t>
         </is>
       </c>
-      <c r="N364" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
+      <c r="N364" t="n">
+        <v>297</v>
       </c>
       <c r="O364" t="inlineStr"/>
       <c r="P364" t="inlineStr">
@@ -39651,10 +39229,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z364" t="inlineStr">
-        <is>
-          <t>172.0</t>
-        </is>
+      <c r="Z364" t="n">
+        <v>172</v>
       </c>
       <c r="AA364" t="inlineStr">
         <is>
@@ -39726,10 +39302,8 @@
           <t>21:14</t>
         </is>
       </c>
-      <c r="N365" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
+      <c r="N365" t="n">
+        <v>2049</v>
       </c>
       <c r="O365" t="inlineStr"/>
       <c r="P365" t="inlineStr">
@@ -39772,10 +39346,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z365" t="inlineStr">
-        <is>
-          <t>967.0</t>
-        </is>
+      <c r="Z365" t="n">
+        <v>967</v>
       </c>
       <c r="AA365" t="inlineStr">
         <is>
@@ -39847,10 +39419,8 @@
           <t>21:45</t>
         </is>
       </c>
-      <c r="N366" t="inlineStr">
-        <is>
-          <t>2145</t>
-        </is>
+      <c r="N366" t="n">
+        <v>2145</v>
       </c>
       <c r="O366" t="inlineStr"/>
       <c r="P366" t="inlineStr">
@@ -39893,10 +39463,8 @@
           <t>M50-54</t>
         </is>
       </c>
-      <c r="Z366" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
+      <c r="Z366" t="n">
+        <v>78</v>
       </c>
       <c r="AA366" t="inlineStr">
         <is>
@@ -39968,10 +39536,8 @@
           <t>22:15</t>
         </is>
       </c>
-      <c r="N367" t="inlineStr">
-        <is>
-          <t>2175</t>
-        </is>
+      <c r="N367" t="n">
+        <v>2175</v>
       </c>
       <c r="O367" t="inlineStr"/>
       <c r="P367" t="inlineStr">
@@ -40014,10 +39580,8 @@
           <t>M60-64</t>
         </is>
       </c>
-      <c r="Z367" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
+      <c r="Z367" t="n">
+        <v>16</v>
       </c>
       <c r="AA367" t="inlineStr">
         <is>
@@ -40089,10 +39653,8 @@
           <t>22:35</t>
         </is>
       </c>
-      <c r="N368" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
+      <c r="N368" t="n">
+        <v>391</v>
       </c>
       <c r="O368" t="inlineStr"/>
       <c r="P368" t="inlineStr">
@@ -40135,10 +39697,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z368" t="inlineStr">
-        <is>
-          <t>229.0</t>
-        </is>
+      <c r="Z368" t="n">
+        <v>229</v>
       </c>
       <c r="AA368" t="inlineStr">
         <is>
@@ -40210,10 +39770,8 @@
           <t>22:21</t>
         </is>
       </c>
-      <c r="N369" t="inlineStr">
-        <is>
-          <t>2305</t>
-        </is>
+      <c r="N369" t="n">
+        <v>2305</v>
       </c>
       <c r="O369" t="inlineStr"/>
       <c r="P369" t="inlineStr">
@@ -40256,10 +39814,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z369" t="inlineStr">
-        <is>
-          <t>1055.0</t>
-        </is>
+      <c r="Z369" t="n">
+        <v>1055</v>
       </c>
       <c r="AA369" t="inlineStr">
         <is>
@@ -40331,10 +39887,8 @@
           <t>22:20</t>
         </is>
       </c>
-      <c r="N370" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
+      <c r="N370" t="n">
+        <v>462</v>
       </c>
       <c r="O370" t="inlineStr"/>
       <c r="P370" t="inlineStr">
@@ -40377,10 +39931,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z370" t="inlineStr">
-        <is>
-          <t>261.0</t>
-        </is>
+      <c r="Z370" t="n">
+        <v>261</v>
       </c>
       <c r="AA370" t="inlineStr">
         <is>
@@ -40452,10 +40004,8 @@
           <t>23:23</t>
         </is>
       </c>
-      <c r="N371" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
+      <c r="N371" t="n">
+        <v>464</v>
       </c>
       <c r="O371" t="inlineStr"/>
       <c r="P371" t="inlineStr">
@@ -40498,10 +40048,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z371" t="inlineStr">
-        <is>
-          <t>263.0</t>
-        </is>
+      <c r="Z371" t="n">
+        <v>263</v>
       </c>
       <c r="AA371" t="inlineStr">
         <is>
@@ -40573,10 +40121,8 @@
           <t>22:53</t>
         </is>
       </c>
-      <c r="N372" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
+      <c r="N372" t="n">
+        <v>3040</v>
       </c>
       <c r="O372" t="inlineStr"/>
       <c r="P372" t="inlineStr">
@@ -40690,10 +40236,8 @@
           <t>23:28</t>
         </is>
       </c>
-      <c r="N373" t="inlineStr">
-        <is>
-          <t>2543</t>
-        </is>
+      <c r="N373" t="n">
+        <v>2543</v>
       </c>
       <c r="O373" t="inlineStr"/>
       <c r="P373" t="inlineStr">
@@ -40736,10 +40280,8 @@
           <t>M60-64</t>
         </is>
       </c>
-      <c r="Z373" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
+      <c r="Z373" t="n">
+        <v>28</v>
       </c>
       <c r="AA373" t="inlineStr">
         <is>
@@ -40811,10 +40353,8 @@
           <t>24:16</t>
         </is>
       </c>
-      <c r="N374" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
+      <c r="N374" t="n">
+        <v>577</v>
       </c>
       <c r="O374" t="inlineStr"/>
       <c r="P374" t="inlineStr">
@@ -40857,10 +40397,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z374" t="inlineStr">
-        <is>
-          <t>315.0</t>
-        </is>
+      <c r="Z374" t="n">
+        <v>315</v>
       </c>
       <c r="AA374" t="inlineStr">
         <is>
@@ -40932,10 +40470,8 @@
           <t>24:18</t>
         </is>
       </c>
-      <c r="N375" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
+      <c r="N375" t="n">
+        <v>599</v>
       </c>
       <c r="O375" t="inlineStr"/>
       <c r="P375" t="inlineStr">
@@ -40978,10 +40514,8 @@
           <t>K40-44</t>
         </is>
       </c>
-      <c r="Z375" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
+      <c r="Z375" t="n">
+        <v>62</v>
       </c>
       <c r="AA375" t="inlineStr">
         <is>
@@ -41053,10 +40587,8 @@
           <t>27:43</t>
         </is>
       </c>
-      <c r="N376" t="inlineStr">
-        <is>
-          <t>979</t>
-        </is>
+      <c r="N376" t="n">
+        <v>979</v>
       </c>
       <c r="O376" t="inlineStr"/>
       <c r="P376" t="inlineStr">
@@ -41099,10 +40631,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z376" t="inlineStr">
-        <is>
-          <t>493.0</t>
-        </is>
+      <c r="Z376" t="n">
+        <v>493</v>
       </c>
       <c r="AA376" t="inlineStr">
         <is>
@@ -41121,6 +40651,301 @@
       </c>
       <c r="AD376" t="inlineStr"/>
       <c r="AE376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>15</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Holmestrand maraton</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Halvmaraton</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>M35-39</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Vegard Henriksen</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr"/>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>1:49:41</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>1:49:41</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr"/>
+      <c r="M377" t="inlineStr"/>
+      <c r="N377" t="n">
+        <v>255</v>
+      </c>
+      <c r="O377" t="inlineStr"/>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>Holmestrand halvmaraton uke 15 manuell registrering</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>manual-2026-04-12-holmestrand-half</t>
+        </is>
+      </c>
+      <c r="R377" t="n">
+        <v>255</v>
+      </c>
+      <c r="S377" t="inlineStr"/>
+      <c r="T377" t="inlineStr"/>
+      <c r="U377" t="inlineStr"/>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>Manuell registrering</t>
+        </is>
+      </c>
+      <c r="W377" t="inlineStr"/>
+      <c r="X377" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y377" t="inlineStr">
+        <is>
+          <t>M35-39</t>
+        </is>
+      </c>
+      <c r="Z377" t="inlineStr"/>
+      <c r="AA377" t="inlineStr"/>
+      <c r="AB377" t="inlineStr"/>
+      <c r="AC377" t="inlineStr"/>
+      <c r="AD377" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE377" t="inlineStr">
+        <is>
+          <t>Halvmaraton</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>15</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Holmestrand maraton</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>K14-15</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Alva Witnes Ertresv?g</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr"/>
+      <c r="H378" t="inlineStr"/>
+      <c r="I378" t="inlineStr"/>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>43:51</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>43:51</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="n">
+        <v>5</v>
+      </c>
+      <c r="O378" t="inlineStr"/>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>Holmestrand 10 km uke 15 manuell registrering</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>manual-2026-04-12-holmestrand-10k</t>
+        </is>
+      </c>
+      <c r="R378" t="n">
+        <v>5</v>
+      </c>
+      <c r="S378" t="inlineStr"/>
+      <c r="T378" t="inlineStr"/>
+      <c r="U378" t="inlineStr"/>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>Manuell registrering</t>
+        </is>
+      </c>
+      <c r="W378" t="inlineStr"/>
+      <c r="X378" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="Y378" t="inlineStr">
+        <is>
+          <t>K14-15</t>
+        </is>
+      </c>
+      <c r="Z378" t="inlineStr"/>
+      <c r="AA378" t="inlineStr"/>
+      <c r="AB378" t="inlineStr"/>
+      <c r="AC378" t="inlineStr"/>
+      <c r="AD378" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="AE378" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>15</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Paris maraton</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Maraton</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>M2F</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Marita Bergum Sandberg</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr"/>
+      <c r="I379" t="inlineStr"/>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>3:38:12</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>3:38:12</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>13054</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>Offisiell resultattid 5:06:39. Nettotid 3:38:12. Guntid 5:06:39.</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>Paris maraton manuell registrering fra tekst</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>manual-2026-04-12-paris-maraton</t>
+        </is>
+      </c>
+      <c r="R379" t="n">
+        <v>13054</v>
+      </c>
+      <c r="S379" t="inlineStr"/>
+      <c r="T379" t="inlineStr"/>
+      <c r="U379" t="inlineStr"/>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>Manuell registrering</t>
+        </is>
+      </c>
+      <c r="W379" t="inlineStr"/>
+      <c r="X379" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="Y379" t="inlineStr">
+        <is>
+          <t>M2F</t>
+        </is>
+      </c>
+      <c r="Z379" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AA379" t="inlineStr"/>
+      <c r="AB379" t="inlineStr"/>
+      <c r="AC379" t="inlineStr"/>
+      <c r="AD379" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="AE379" t="inlineStr">
+        <is>
+          <t>Maraton</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/arbeidsfiler/weekly_results_2026.xlsx
+++ b/data/arbeidsfiler/weekly_results_2026.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE379"/>
+  <dimension ref="A1:AE381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40886,10 +40886,8 @@
       </c>
       <c r="L379" t="inlineStr"/>
       <c r="M379" t="inlineStr"/>
-      <c r="N379" t="inlineStr">
-        <is>
-          <t>13054</t>
-        </is>
+      <c r="N379" t="n">
+        <v>13054</v>
       </c>
       <c r="O379" t="inlineStr">
         <is>
@@ -40928,10 +40926,8 @@
           <t>M2F</t>
         </is>
       </c>
-      <c r="Z379" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
+      <c r="Z379" t="n">
+        <v>132</v>
       </c>
       <c r="AA379" t="inlineStr"/>
       <c r="AB379" t="inlineStr"/>
@@ -40942,6 +40938,206 @@
         </is>
       </c>
       <c r="AE379" t="inlineStr">
+        <is>
+          <t>Maraton</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>15</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Cherry Blossom 10 Mile</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>10 mile</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>M40-44</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Bj?rnar Slettv?g</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr"/>
+      <c r="I380" t="inlineStr"/>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>55:32</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>55:32</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="n">
+        <v>172</v>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>Klasseplass 8. M-rangering 144. BIB 281.</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>Cherry Blossom 10 Mile manuell registrering fra bilde</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>manual-2026-04-12-cherry-blossom-10-mile</t>
+        </is>
+      </c>
+      <c r="R380" t="n">
+        <v>172</v>
+      </c>
+      <c r="S380" t="inlineStr"/>
+      <c r="T380" t="inlineStr"/>
+      <c r="U380" t="inlineStr"/>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>Manuell registrering</t>
+        </is>
+      </c>
+      <c r="W380" t="inlineStr"/>
+      <c r="X380" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y380" t="inlineStr">
+        <is>
+          <t>M40-44</t>
+        </is>
+      </c>
+      <c r="Z380" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA380" t="inlineStr"/>
+      <c r="AB380" t="inlineStr"/>
+      <c r="AC380" t="inlineStr"/>
+      <c r="AD380" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE380" t="inlineStr">
+        <is>
+          <t>10 mile</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>15</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Milano Marathon</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Maraton</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Martin Stray Egeberg</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr"/>
+      <c r="H381" t="inlineStr"/>
+      <c r="I381" t="inlineStr"/>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>2:32:43</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>2:32:43</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr"/>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>Manuell registrering fra tekst. BIB 11436. NC.</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>Milano Marathon manuell registrering fra tekst</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>manual-2026-04-12-milano-marathon-martin</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr"/>
+      <c r="S381" t="inlineStr"/>
+      <c r="T381" t="inlineStr"/>
+      <c r="U381" t="inlineStr"/>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>Manuell registrering</t>
+        </is>
+      </c>
+      <c r="W381" t="inlineStr"/>
+      <c r="X381" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y381" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="Z381" t="inlineStr"/>
+      <c r="AA381" t="inlineStr">
+        <is>
+          <t>1:15:16</t>
+        </is>
+      </c>
+      <c r="AB381" t="inlineStr"/>
+      <c r="AC381" t="inlineStr"/>
+      <c r="AD381" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE381" t="inlineStr">
         <is>
           <t>Maraton</t>
         </is>

--- a/data/arbeidsfiler/weekly_results_2026.xlsx
+++ b/data/arbeidsfiler/weekly_results_2026.xlsx
@@ -26164,7 +26164,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Holmestrand maraton 5k</t>
+          <t>Holmestrand maraton</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -26203,7 +26203,7 @@
       <c r="O252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Holmestrand maraton 5k uke 15 manuell registrering</t>
+          <t>Holmestrand maraton uke 15 manuell registrering</t>
         </is>
       </c>
       <c r="Q252" t="inlineStr">

--- a/data/arbeidsfiler/weekly_results_2026.xlsx
+++ b/data/arbeidsfiler/weekly_results_2026.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE381"/>
+  <dimension ref="A1:AE382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27185,10 +27185,8 @@
           <t>15:32</t>
         </is>
       </c>
-      <c r="N262" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
+      <c r="N262" t="n">
+        <v>38</v>
       </c>
       <c r="O262" t="inlineStr"/>
       <c r="P262" t="inlineStr">
@@ -27231,10 +27229,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
+      <c r="Z262" t="n">
+        <v>27</v>
       </c>
       <c r="AA262" t="inlineStr">
         <is>
@@ -27306,10 +27302,8 @@
           <t>19:28</t>
         </is>
       </c>
-      <c r="N263" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
+      <c r="N263" t="n">
+        <v>42</v>
       </c>
       <c r="O263" t="inlineStr"/>
       <c r="P263" t="inlineStr">
@@ -27352,10 +27346,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="Z263" t="n">
+        <v>30</v>
       </c>
       <c r="AA263" t="inlineStr">
         <is>
@@ -27427,10 +27419,8 @@
           <t>15:39</t>
         </is>
       </c>
-      <c r="N264" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="N264" t="n">
+        <v>49</v>
       </c>
       <c r="O264" t="inlineStr"/>
       <c r="P264" t="inlineStr">
@@ -27473,10 +27463,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
+      <c r="Z264" t="n">
+        <v>6</v>
       </c>
       <c r="AA264" t="inlineStr">
         <is>
@@ -27548,10 +27536,8 @@
           <t>15:45</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="N265" t="n">
+        <v>50</v>
       </c>
       <c r="O265" t="inlineStr"/>
       <c r="P265" t="inlineStr">
@@ -27594,10 +27580,8 @@
           <t>M18-19</t>
         </is>
       </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="Z265" t="n">
+        <v>4</v>
       </c>
       <c r="AA265" t="inlineStr">
         <is>
@@ -27669,10 +27653,8 @@
           <t>15:32</t>
         </is>
       </c>
-      <c r="N266" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
+      <c r="N266" t="n">
+        <v>61</v>
       </c>
       <c r="O266" t="inlineStr"/>
       <c r="P266" t="inlineStr">
@@ -27715,10 +27697,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
+      <c r="Z266" t="n">
+        <v>42</v>
       </c>
       <c r="AA266" t="inlineStr">
         <is>
@@ -27790,10 +27770,8 @@
           <t>15:50</t>
         </is>
       </c>
-      <c r="N267" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="N267" t="n">
+        <v>86</v>
       </c>
       <c r="O267" t="inlineStr"/>
       <c r="P267" t="inlineStr">
@@ -27836,10 +27814,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
+      <c r="Z267" t="n">
+        <v>11</v>
       </c>
       <c r="AA267" t="inlineStr">
         <is>
@@ -27911,10 +27887,8 @@
           <t>16:06</t>
         </is>
       </c>
-      <c r="N268" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="N268" t="n">
+        <v>92</v>
       </c>
       <c r="O268" t="inlineStr"/>
       <c r="P268" t="inlineStr">
@@ -27957,10 +27931,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>59.0</t>
-        </is>
+      <c r="Z268" t="n">
+        <v>59</v>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
@@ -28032,10 +28004,8 @@
           <t>16:05</t>
         </is>
       </c>
-      <c r="N269" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
+      <c r="N269" t="n">
+        <v>107</v>
       </c>
       <c r="O269" t="inlineStr"/>
       <c r="P269" t="inlineStr">
@@ -28078,10 +28048,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>9.0</t>
-        </is>
+      <c r="Z269" t="n">
+        <v>9</v>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
@@ -28153,10 +28121,8 @@
           <t>16:14</t>
         </is>
       </c>
-      <c r="N270" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
+      <c r="N270" t="n">
+        <v>116</v>
       </c>
       <c r="O270" t="inlineStr"/>
       <c r="P270" t="inlineStr">
@@ -28199,10 +28165,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
+      <c r="Z270" t="n">
+        <v>11</v>
       </c>
       <c r="AA270" t="inlineStr">
         <is>
@@ -28274,10 +28238,8 @@
           <t>16:18</t>
         </is>
       </c>
-      <c r="N271" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="N271" t="n">
+        <v>4</v>
       </c>
       <c r="O271" t="inlineStr"/>
       <c r="P271" t="inlineStr">
@@ -28320,10 +28282,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="Z271" t="n">
+        <v>2</v>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
@@ -28395,10 +28355,8 @@
           <t>16:23</t>
         </is>
       </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
+      <c r="N272" t="n">
+        <v>127</v>
       </c>
       <c r="O272" t="inlineStr"/>
       <c r="P272" t="inlineStr">
@@ -28441,10 +28399,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
+      <c r="Z272" t="n">
+        <v>77</v>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
@@ -28516,10 +28472,8 @@
           <t>16:33</t>
         </is>
       </c>
-      <c r="N273" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
+      <c r="N273" t="n">
+        <v>133</v>
       </c>
       <c r="O273" t="inlineStr"/>
       <c r="P273" t="inlineStr">
@@ -28562,10 +28516,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z273" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
+      <c r="Z273" t="n">
+        <v>81</v>
       </c>
       <c r="AA273" t="inlineStr">
         <is>
@@ -28637,10 +28589,8 @@
           <t>16:33</t>
         </is>
       </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
+      <c r="N274" t="n">
+        <v>141</v>
       </c>
       <c r="O274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
@@ -28754,10 +28704,8 @@
           <t>16:22</t>
         </is>
       </c>
-      <c r="N275" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
+      <c r="N275" t="n">
+        <v>142</v>
       </c>
       <c r="O275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
@@ -28800,10 +28748,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z275" t="inlineStr">
-        <is>
-          <t>27.0</t>
-        </is>
+      <c r="Z275" t="n">
+        <v>27</v>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
@@ -28875,10 +28821,8 @@
           <t>16:20</t>
         </is>
       </c>
-      <c r="N276" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
+      <c r="N276" t="n">
+        <v>144</v>
       </c>
       <c r="O276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
@@ -28921,10 +28865,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
+      <c r="Z276" t="n">
+        <v>85</v>
       </c>
       <c r="AA276" t="inlineStr">
         <is>
@@ -28996,10 +28938,8 @@
           <t>16:28</t>
         </is>
       </c>
-      <c r="N277" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
+      <c r="N277" t="n">
+        <v>149</v>
       </c>
       <c r="O277" t="inlineStr"/>
       <c r="P277" t="inlineStr">
@@ -29042,10 +28982,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
+      <c r="Z277" t="n">
+        <v>87</v>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
@@ -29117,10 +29055,8 @@
           <t>16:42</t>
         </is>
       </c>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
+      <c r="N278" t="n">
+        <v>179</v>
       </c>
       <c r="O278" t="inlineStr"/>
       <c r="P278" t="inlineStr">
@@ -29163,10 +29099,8 @@
           <t>M45-49</t>
         </is>
       </c>
-      <c r="Z278" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
+      <c r="Z278" t="n">
+        <v>6</v>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
@@ -29238,10 +29172,8 @@
           <t>16:34</t>
         </is>
       </c>
-      <c r="N279" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
+      <c r="N279" t="n">
+        <v>200</v>
       </c>
       <c r="O279" t="inlineStr"/>
       <c r="P279" t="inlineStr">
@@ -29284,10 +29216,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z279" t="inlineStr">
-        <is>
-          <t>118.0</t>
-        </is>
+      <c r="Z279" t="n">
+        <v>118</v>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
@@ -29359,10 +29289,8 @@
           <t>16:40</t>
         </is>
       </c>
-      <c r="N280" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
+      <c r="N280" t="n">
+        <v>212</v>
       </c>
       <c r="O280" t="inlineStr"/>
       <c r="P280" t="inlineStr">
@@ -29476,10 +29404,8 @@
           <t>16:44</t>
         </is>
       </c>
-      <c r="N281" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
+      <c r="N281" t="n">
+        <v>201</v>
       </c>
       <c r="O281" t="inlineStr"/>
       <c r="P281" t="inlineStr">
@@ -29522,10 +29448,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z281" t="inlineStr">
-        <is>
-          <t>119.0</t>
-        </is>
+      <c r="Z281" t="n">
+        <v>119</v>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
@@ -29597,10 +29521,8 @@
           <t>17:06</t>
         </is>
       </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
+      <c r="N282" t="n">
+        <v>213</v>
       </c>
       <c r="O282" t="inlineStr"/>
       <c r="P282" t="inlineStr">
@@ -29643,10 +29565,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z282" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
+      <c r="Z282" t="n">
+        <v>128</v>
       </c>
       <c r="AA282" t="inlineStr">
         <is>
@@ -29718,10 +29638,8 @@
           <t>17:06</t>
         </is>
       </c>
-      <c r="N283" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
+      <c r="N283" t="n">
+        <v>220</v>
       </c>
       <c r="O283" t="inlineStr"/>
       <c r="P283" t="inlineStr">
@@ -29764,10 +29682,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z283" t="inlineStr">
-        <is>
-          <t>130.0</t>
-        </is>
+      <c r="Z283" t="n">
+        <v>130</v>
       </c>
       <c r="AA283" t="inlineStr">
         <is>
@@ -29839,10 +29755,8 @@
           <t>16:08</t>
         </is>
       </c>
-      <c r="N284" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
+      <c r="N284" t="n">
+        <v>238</v>
       </c>
       <c r="O284" t="inlineStr"/>
       <c r="P284" t="inlineStr">
@@ -29956,10 +29870,8 @@
           <t>17:08</t>
         </is>
       </c>
-      <c r="N285" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
+      <c r="N285" t="n">
+        <v>227</v>
       </c>
       <c r="O285" t="inlineStr"/>
       <c r="P285" t="inlineStr">
@@ -30002,10 +29914,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z285" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
+      <c r="Z285" t="n">
+        <v>21</v>
       </c>
       <c r="AA285" t="inlineStr">
         <is>
@@ -30077,10 +29987,8 @@
           <t>16:55</t>
         </is>
       </c>
-      <c r="N286" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
+      <c r="N286" t="n">
+        <v>228</v>
       </c>
       <c r="O286" t="inlineStr"/>
       <c r="P286" t="inlineStr">
@@ -30123,10 +30031,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z286" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
+      <c r="Z286" t="n">
+        <v>45</v>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
@@ -30198,10 +30104,8 @@
           <t>17:06</t>
         </is>
       </c>
-      <c r="N287" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
+      <c r="N287" t="n">
+        <v>251</v>
       </c>
       <c r="O287" t="inlineStr"/>
       <c r="P287" t="inlineStr">
@@ -30244,10 +30148,8 @@
           <t>M45-49</t>
         </is>
       </c>
-      <c r="Z287" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
+      <c r="Z287" t="n">
+        <v>10</v>
       </c>
       <c r="AA287" t="inlineStr">
         <is>
@@ -30319,10 +30221,8 @@
           <t>17:07</t>
         </is>
       </c>
-      <c r="N288" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
+      <c r="N288" t="n">
+        <v>258</v>
       </c>
       <c r="O288" t="inlineStr"/>
       <c r="P288" t="inlineStr">
@@ -30365,10 +30265,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z288" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
+      <c r="Z288" t="n">
+        <v>25</v>
       </c>
       <c r="AA288" t="inlineStr">
         <is>
@@ -30440,10 +30338,8 @@
           <t>17:18</t>
         </is>
       </c>
-      <c r="N289" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
+      <c r="N289" t="n">
+        <v>261</v>
       </c>
       <c r="O289" t="inlineStr"/>
       <c r="P289" t="inlineStr">
@@ -30486,10 +30382,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z289" t="inlineStr">
-        <is>
-          <t>149.0</t>
-        </is>
+      <c r="Z289" t="n">
+        <v>149</v>
       </c>
       <c r="AA289" t="inlineStr">
         <is>
@@ -30561,10 +30455,8 @@
           <t>17:08</t>
         </is>
       </c>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+      <c r="N290" t="n">
+        <v>269</v>
       </c>
       <c r="O290" t="inlineStr"/>
       <c r="P290" t="inlineStr">
@@ -30607,10 +30499,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z290" t="inlineStr">
-        <is>
-          <t>58.0</t>
-        </is>
+      <c r="Z290" t="n">
+        <v>58</v>
       </c>
       <c r="AA290" t="inlineStr">
         <is>
@@ -30682,10 +30572,8 @@
           <t>16:55</t>
         </is>
       </c>
-      <c r="N291" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
+      <c r="N291" t="n">
+        <v>270</v>
       </c>
       <c r="O291" t="inlineStr"/>
       <c r="P291" t="inlineStr">
@@ -30728,10 +30616,8 @@
           <t>M45-49</t>
         </is>
       </c>
-      <c r="Z291" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
+      <c r="Z291" t="n">
+        <v>11</v>
       </c>
       <c r="AA291" t="inlineStr">
         <is>
@@ -30803,10 +30689,8 @@
           <t>17:04</t>
         </is>
       </c>
-      <c r="N292" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
+      <c r="N292" t="n">
+        <v>277</v>
       </c>
       <c r="O292" t="inlineStr"/>
       <c r="P292" t="inlineStr">
@@ -30849,10 +30733,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z292" t="inlineStr">
-        <is>
-          <t>157.0</t>
-        </is>
+      <c r="Z292" t="n">
+        <v>157</v>
       </c>
       <c r="AA292" t="inlineStr">
         <is>
@@ -30924,10 +30806,8 @@
           <t>16:55</t>
         </is>
       </c>
-      <c r="N293" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="N293" t="n">
+        <v>14</v>
       </c>
       <c r="O293" t="inlineStr"/>
       <c r="P293" t="inlineStr">
@@ -30970,10 +30850,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z293" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
+      <c r="Z293" t="n">
+        <v>10</v>
       </c>
       <c r="AA293" t="inlineStr">
         <is>
@@ -31045,10 +30923,8 @@
           <t>17:20</t>
         </is>
       </c>
-      <c r="N294" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
+      <c r="N294" t="n">
+        <v>294</v>
       </c>
       <c r="O294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
@@ -31091,10 +30967,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z294" t="inlineStr">
-        <is>
-          <t>168.0</t>
-        </is>
+      <c r="Z294" t="n">
+        <v>168</v>
       </c>
       <c r="AA294" t="inlineStr">
         <is>
@@ -31166,10 +31040,8 @@
           <t>17:19</t>
         </is>
       </c>
-      <c r="N295" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="N295" t="n">
+        <v>17</v>
       </c>
       <c r="O295" t="inlineStr"/>
       <c r="P295" t="inlineStr">
@@ -31212,10 +31084,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z295" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
+      <c r="Z295" t="n">
+        <v>11</v>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
@@ -31287,10 +31157,8 @@
           <t>17:22</t>
         </is>
       </c>
-      <c r="N296" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
+      <c r="N296" t="n">
+        <v>18</v>
       </c>
       <c r="O296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
@@ -31333,10 +31201,8 @@
           <t>K35-39</t>
         </is>
       </c>
-      <c r="Z296" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="Z296" t="n">
+        <v>3</v>
       </c>
       <c r="AA296" t="inlineStr">
         <is>
@@ -31408,10 +31274,8 @@
           <t>17:03</t>
         </is>
       </c>
-      <c r="N297" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
+      <c r="N297" t="n">
+        <v>320</v>
       </c>
       <c r="O297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
@@ -31454,10 +31318,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z297" t="inlineStr">
-        <is>
-          <t>184.0</t>
-        </is>
+      <c r="Z297" t="n">
+        <v>184</v>
       </c>
       <c r="AA297" t="inlineStr">
         <is>
@@ -31529,10 +31391,8 @@
           <t>16:37</t>
         </is>
       </c>
-      <c r="N298" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="N298" t="n">
+        <v>20</v>
       </c>
       <c r="O298" t="inlineStr"/>
       <c r="P298" t="inlineStr">
@@ -31575,10 +31435,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z298" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
+      <c r="Z298" t="n">
+        <v>13</v>
       </c>
       <c r="AA298" t="inlineStr">
         <is>
@@ -31650,10 +31508,8 @@
           <t>17:04</t>
         </is>
       </c>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
+      <c r="N299" t="n">
+        <v>331</v>
       </c>
       <c r="O299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
@@ -31696,10 +31552,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z299" t="inlineStr">
-        <is>
-          <t>191.0</t>
-        </is>
+      <c r="Z299" t="n">
+        <v>191</v>
       </c>
       <c r="AA299" t="inlineStr">
         <is>
@@ -31771,10 +31625,8 @@
           <t>17:15</t>
         </is>
       </c>
-      <c r="N300" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
+      <c r="N300" t="n">
+        <v>339</v>
       </c>
       <c r="O300" t="inlineStr"/>
       <c r="P300" t="inlineStr">
@@ -31817,10 +31669,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z300" t="inlineStr">
-        <is>
-          <t>196.0</t>
-        </is>
+      <c r="Z300" t="n">
+        <v>196</v>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
@@ -31892,10 +31742,8 @@
           <t>17:30</t>
         </is>
       </c>
-      <c r="N301" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
+      <c r="N301" t="n">
+        <v>345</v>
       </c>
       <c r="O301" t="inlineStr"/>
       <c r="P301" t="inlineStr">
@@ -31938,10 +31786,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z301" t="inlineStr">
-        <is>
-          <t>201.0</t>
-        </is>
+      <c r="Z301" t="n">
+        <v>201</v>
       </c>
       <c r="AA301" t="inlineStr">
         <is>
@@ -32013,10 +31859,8 @@
           <t>17:22</t>
         </is>
       </c>
-      <c r="N302" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="N302" t="n">
+        <v>23</v>
       </c>
       <c r="O302" t="inlineStr"/>
       <c r="P302" t="inlineStr">
@@ -32059,10 +31903,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z302" t="inlineStr">
-        <is>
-          <t>14.0</t>
-        </is>
+      <c r="Z302" t="n">
+        <v>14</v>
       </c>
       <c r="AA302" t="inlineStr">
         <is>
@@ -32134,10 +31976,8 @@
           <t>17:22</t>
         </is>
       </c>
-      <c r="N303" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="N303" t="n">
+        <v>24</v>
       </c>
       <c r="O303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
@@ -32180,10 +32020,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z303" t="inlineStr">
-        <is>
-          <t>15.0</t>
-        </is>
+      <c r="Z303" t="n">
+        <v>15</v>
       </c>
       <c r="AA303" t="inlineStr">
         <is>
@@ -32255,10 +32093,8 @@
           <t>17:43</t>
         </is>
       </c>
-      <c r="N304" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
+      <c r="N304" t="n">
+        <v>405</v>
       </c>
       <c r="O304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
@@ -32301,10 +32137,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z304" t="inlineStr">
-        <is>
-          <t>230.0</t>
-        </is>
+      <c r="Z304" t="n">
+        <v>230</v>
       </c>
       <c r="AA304" t="inlineStr">
         <is>
@@ -32376,10 +32210,8 @@
           <t>17:40</t>
         </is>
       </c>
-      <c r="N305" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
+      <c r="N305" t="n">
+        <v>411</v>
       </c>
       <c r="O305" t="inlineStr"/>
       <c r="P305" t="inlineStr">
@@ -32422,10 +32254,8 @@
           <t>M18-19</t>
         </is>
       </c>
-      <c r="Z305" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
+      <c r="Z305" t="n">
+        <v>10</v>
       </c>
       <c r="AA305" t="inlineStr">
         <is>
@@ -32497,10 +32327,8 @@
           <t>17:43</t>
         </is>
       </c>
-      <c r="N306" t="inlineStr">
-        <is>
-          <t>418</t>
-        </is>
+      <c r="N306" t="n">
+        <v>418</v>
       </c>
       <c r="O306" t="inlineStr"/>
       <c r="P306" t="inlineStr">
@@ -32543,10 +32371,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z306" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
+      <c r="Z306" t="n">
+        <v>92</v>
       </c>
       <c r="AA306" t="inlineStr">
         <is>
@@ -32618,10 +32444,8 @@
           <t>17:18</t>
         </is>
       </c>
-      <c r="N307" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
+      <c r="N307" t="n">
+        <v>422</v>
       </c>
       <c r="O307" t="inlineStr"/>
       <c r="P307" t="inlineStr">
@@ -32664,10 +32488,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z307" t="inlineStr">
-        <is>
-          <t>242.0</t>
-        </is>
+      <c r="Z307" t="n">
+        <v>242</v>
       </c>
       <c r="AA307" t="inlineStr">
         <is>
@@ -32739,10 +32561,8 @@
           <t>18:18</t>
         </is>
       </c>
-      <c r="N308" t="inlineStr">
-        <is>
-          <t>471</t>
-        </is>
+      <c r="N308" t="n">
+        <v>471</v>
       </c>
       <c r="O308" t="inlineStr"/>
       <c r="P308" t="inlineStr">
@@ -32785,10 +32605,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z308" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
+      <c r="Z308" t="n">
+        <v>102</v>
       </c>
       <c r="AA308" t="inlineStr">
         <is>
@@ -32860,10 +32678,8 @@
           <t>17:58</t>
         </is>
       </c>
-      <c r="N309" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
+      <c r="N309" t="n">
+        <v>32</v>
       </c>
       <c r="O309" t="inlineStr"/>
       <c r="P309" t="inlineStr">
@@ -32906,10 +32722,8 @@
           <t>K20-22</t>
         </is>
       </c>
-      <c r="Z309" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
+      <c r="Z309" t="n">
+        <v>7</v>
       </c>
       <c r="AA309" t="inlineStr">
         <is>
@@ -32981,10 +32795,8 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="N310" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
+      <c r="N310" t="n">
+        <v>506</v>
       </c>
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
@@ -33027,10 +32839,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z310" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
+      <c r="Z310" t="n">
+        <v>110</v>
       </c>
       <c r="AA310" t="inlineStr">
         <is>
@@ -33102,10 +32912,8 @@
           <t>17:46</t>
         </is>
       </c>
-      <c r="N311" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
+      <c r="N311" t="n">
+        <v>523</v>
       </c>
       <c r="O311" t="inlineStr"/>
       <c r="P311" t="inlineStr">
@@ -33148,10 +32956,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z311" t="inlineStr">
-        <is>
-          <t>298.0</t>
-        </is>
+      <c r="Z311" t="n">
+        <v>298</v>
       </c>
       <c r="AA311" t="inlineStr">
         <is>
@@ -33223,10 +33029,8 @@
           <t>18:13</t>
         </is>
       </c>
-      <c r="N312" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
+      <c r="N312" t="n">
+        <v>604</v>
       </c>
       <c r="O312" t="inlineStr"/>
       <c r="P312" t="inlineStr">
@@ -33269,10 +33073,8 @@
           <t>M55-59</t>
         </is>
       </c>
-      <c r="Z312" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="Z312" t="n">
+        <v>5</v>
       </c>
       <c r="AA312" t="inlineStr">
         <is>
@@ -33344,10 +33146,8 @@
           <t>18:25</t>
         </is>
       </c>
-      <c r="N313" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
+      <c r="N313" t="n">
+        <v>630</v>
       </c>
       <c r="O313" t="inlineStr"/>
       <c r="P313" t="inlineStr">
@@ -33390,10 +33190,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z313" t="inlineStr">
-        <is>
-          <t>349.0</t>
-        </is>
+      <c r="Z313" t="n">
+        <v>349</v>
       </c>
       <c r="AA313" t="inlineStr">
         <is>
@@ -33465,10 +33263,8 @@
           <t>18:21</t>
         </is>
       </c>
-      <c r="N314" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
+      <c r="N314" t="n">
+        <v>640</v>
       </c>
       <c r="O314" t="inlineStr"/>
       <c r="P314" t="inlineStr">
@@ -33511,10 +33307,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z314" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
+      <c r="Z314" t="n">
+        <v>143</v>
       </c>
       <c r="AA314" t="inlineStr">
         <is>
@@ -33586,10 +33380,8 @@
           <t>18:33</t>
         </is>
       </c>
-      <c r="N315" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
+      <c r="N315" t="n">
+        <v>688</v>
       </c>
       <c r="O315" t="inlineStr"/>
       <c r="P315" t="inlineStr">
@@ -33632,10 +33424,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z315" t="inlineStr">
-        <is>
-          <t>155.0</t>
-        </is>
+      <c r="Z315" t="n">
+        <v>155</v>
       </c>
       <c r="AA315" t="inlineStr">
         <is>
@@ -33707,10 +33497,8 @@
           <t>18:35</t>
         </is>
       </c>
-      <c r="N316" t="inlineStr">
-        <is>
-          <t>691</t>
-        </is>
+      <c r="N316" t="n">
+        <v>691</v>
       </c>
       <c r="O316" t="inlineStr"/>
       <c r="P316" t="inlineStr">
@@ -33753,10 +33541,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z316" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
+      <c r="Z316" t="n">
+        <v>66</v>
       </c>
       <c r="AA316" t="inlineStr">
         <is>
@@ -33828,10 +33614,8 @@
           <t>18:33</t>
         </is>
       </c>
-      <c r="N317" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
+      <c r="N317" t="n">
+        <v>693</v>
       </c>
       <c r="O317" t="inlineStr"/>
       <c r="P317" t="inlineStr">
@@ -33874,10 +33658,8 @@
           <t>M60-64</t>
         </is>
       </c>
-      <c r="Z317" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="Z317" t="n">
+        <v>1</v>
       </c>
       <c r="AA317" t="inlineStr">
         <is>
@@ -33949,10 +33731,8 @@
           <t>18:40</t>
         </is>
       </c>
-      <c r="N318" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+      <c r="N318" t="n">
+        <v>46</v>
       </c>
       <c r="O318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
@@ -33995,10 +33775,8 @@
           <t>K35-39</t>
         </is>
       </c>
-      <c r="Z318" t="inlineStr">
-        <is>
-          <t>11.0</t>
-        </is>
+      <c r="Z318" t="n">
+        <v>11</v>
       </c>
       <c r="AA318" t="inlineStr">
         <is>
@@ -34070,10 +33848,8 @@
           <t>18:38</t>
         </is>
       </c>
-      <c r="N319" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
+      <c r="N319" t="n">
+        <v>768</v>
       </c>
       <c r="O319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
@@ -34116,10 +33892,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z319" t="inlineStr">
-        <is>
-          <t>416.0</t>
-        </is>
+      <c r="Z319" t="n">
+        <v>416</v>
       </c>
       <c r="AA319" t="inlineStr">
         <is>
@@ -34191,10 +33965,8 @@
           <t>18:48</t>
         </is>
       </c>
-      <c r="N320" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
+      <c r="N320" t="n">
+        <v>769</v>
       </c>
       <c r="O320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
@@ -34237,10 +34009,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z320" t="inlineStr">
-        <is>
-          <t>417.0</t>
-        </is>
+      <c r="Z320" t="n">
+        <v>417</v>
       </c>
       <c r="AA320" t="inlineStr">
         <is>
@@ -34312,10 +34082,8 @@
           <t>19:05</t>
         </is>
       </c>
-      <c r="N321" t="inlineStr">
-        <is>
-          <t>800</t>
-        </is>
+      <c r="N321" t="n">
+        <v>800</v>
       </c>
       <c r="O321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
@@ -34358,10 +34126,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z321" t="inlineStr">
-        <is>
-          <t>430.0</t>
-        </is>
+      <c r="Z321" t="n">
+        <v>430</v>
       </c>
       <c r="AA321" t="inlineStr">
         <is>
@@ -34433,10 +34199,8 @@
           <t>19:02</t>
         </is>
       </c>
-      <c r="N322" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
+      <c r="N322" t="n">
+        <v>818</v>
       </c>
       <c r="O322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
@@ -34479,10 +34243,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z322" t="inlineStr">
-        <is>
-          <t>441.0</t>
-        </is>
+      <c r="Z322" t="n">
+        <v>441</v>
       </c>
       <c r="AA322" t="inlineStr">
         <is>
@@ -34554,10 +34316,8 @@
           <t>18:52</t>
         </is>
       </c>
-      <c r="N323" t="inlineStr">
-        <is>
-          <t>820</t>
-        </is>
+      <c r="N323" t="n">
+        <v>820</v>
       </c>
       <c r="O323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
@@ -34600,10 +34360,8 @@
           <t>M60-64</t>
         </is>
       </c>
-      <c r="Z323" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="Z323" t="n">
+        <v>3</v>
       </c>
       <c r="AA323" t="inlineStr">
         <is>
@@ -34675,10 +34433,8 @@
           <t>18:34</t>
         </is>
       </c>
-      <c r="N324" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
+      <c r="N324" t="n">
+        <v>825</v>
       </c>
       <c r="O324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
@@ -34721,10 +34477,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z324" t="inlineStr">
-        <is>
-          <t>187.0</t>
-        </is>
+      <c r="Z324" t="n">
+        <v>187</v>
       </c>
       <c r="AA324" t="inlineStr">
         <is>
@@ -34796,10 +34550,8 @@
           <t>18:53</t>
         </is>
       </c>
-      <c r="N325" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
+      <c r="N325" t="n">
+        <v>871</v>
       </c>
       <c r="O325" t="inlineStr"/>
       <c r="P325" t="inlineStr">
@@ -34842,10 +34594,8 @@
           <t>M60-64</t>
         </is>
       </c>
-      <c r="Z325" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="Z325" t="n">
+        <v>4</v>
       </c>
       <c r="AA325" t="inlineStr">
         <is>
@@ -34917,10 +34667,8 @@
           <t>18:37</t>
         </is>
       </c>
-      <c r="N326" t="inlineStr">
-        <is>
-          <t>954</t>
-        </is>
+      <c r="N326" t="n">
+        <v>954</v>
       </c>
       <c r="O326" t="inlineStr"/>
       <c r="P326" t="inlineStr">
@@ -35034,10 +34782,8 @@
           <t>19:04</t>
         </is>
       </c>
-      <c r="N327" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
+      <c r="N327" t="n">
+        <v>903</v>
       </c>
       <c r="O327" t="inlineStr"/>
       <c r="P327" t="inlineStr">
@@ -35080,10 +34826,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z327" t="inlineStr">
-        <is>
-          <t>492.0</t>
-        </is>
+      <c r="Z327" t="n">
+        <v>492</v>
       </c>
       <c r="AA327" t="inlineStr">
         <is>
@@ -35155,10 +34899,8 @@
           <t>19:10</t>
         </is>
       </c>
-      <c r="N328" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="N328" t="n">
+        <v>66</v>
       </c>
       <c r="O328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
@@ -35201,10 +34943,8 @@
           <t>K45-49</t>
         </is>
       </c>
-      <c r="Z328" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="Z328" t="n">
+        <v>1</v>
       </c>
       <c r="AA328" t="inlineStr">
         <is>
@@ -35276,10 +35016,8 @@
           <t>19:11</t>
         </is>
       </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="N329" t="n">
+        <v>67</v>
       </c>
       <c r="O329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
@@ -35322,10 +35060,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z329" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
+      <c r="Z329" t="n">
+        <v>38</v>
       </c>
       <c r="AA329" t="inlineStr">
         <is>
@@ -35397,10 +35133,8 @@
           <t>18:53</t>
         </is>
       </c>
-      <c r="N330" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
+      <c r="N330" t="n">
+        <v>74</v>
       </c>
       <c r="O330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
@@ -35443,10 +35177,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z330" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
+      <c r="Z330" t="n">
+        <v>43</v>
       </c>
       <c r="AA330" t="inlineStr">
         <is>
@@ -35518,10 +35250,8 @@
           <t>19:08</t>
         </is>
       </c>
-      <c r="N331" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
+      <c r="N331" t="n">
+        <v>968</v>
       </c>
       <c r="O331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
@@ -35564,10 +35294,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z331" t="inlineStr">
-        <is>
-          <t>524.0</t>
-        </is>
+      <c r="Z331" t="n">
+        <v>524</v>
       </c>
       <c r="AA331" t="inlineStr">
         <is>
@@ -35639,10 +35367,8 @@
           <t>18:58</t>
         </is>
       </c>
-      <c r="N332" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
+      <c r="N332" t="n">
+        <v>81</v>
       </c>
       <c r="O332" t="inlineStr"/>
       <c r="P332" t="inlineStr">
@@ -35685,10 +35411,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z332" t="inlineStr">
-        <is>
-          <t>46.0</t>
-        </is>
+      <c r="Z332" t="n">
+        <v>46</v>
       </c>
       <c r="AA332" t="inlineStr">
         <is>
@@ -35760,10 +35484,8 @@
           <t>19:09</t>
         </is>
       </c>
-      <c r="N333" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="N333" t="n">
+        <v>84</v>
       </c>
       <c r="O333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
@@ -35806,10 +35528,8 @@
           <t>K35-39</t>
         </is>
       </c>
-      <c r="Z333" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
+      <c r="Z333" t="n">
+        <v>20</v>
       </c>
       <c r="AA333" t="inlineStr">
         <is>
@@ -35881,10 +35601,8 @@
           <t>19:30</t>
         </is>
       </c>
-      <c r="N334" t="inlineStr">
-        <is>
-          <t>1078</t>
-        </is>
+      <c r="N334" t="n">
+        <v>1078</v>
       </c>
       <c r="O334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
@@ -35927,10 +35645,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z334" t="inlineStr">
-        <is>
-          <t>569.0</t>
-        </is>
+      <c r="Z334" t="n">
+        <v>569</v>
       </c>
       <c r="AA334" t="inlineStr">
         <is>
@@ -36002,10 +35718,8 @@
           <t>19:45</t>
         </is>
       </c>
-      <c r="N335" t="inlineStr">
-        <is>
-          <t>1098</t>
-        </is>
+      <c r="N335" t="n">
+        <v>1098</v>
       </c>
       <c r="O335" t="inlineStr"/>
       <c r="P335" t="inlineStr">
@@ -36048,10 +35762,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z335" t="inlineStr">
-        <is>
-          <t>238.0</t>
-        </is>
+      <c r="Z335" t="n">
+        <v>238</v>
       </c>
       <c r="AA335" t="inlineStr">
         <is>
@@ -36123,10 +35835,8 @@
           <t>18:51</t>
         </is>
       </c>
-      <c r="N336" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
+      <c r="N336" t="n">
+        <v>1122</v>
       </c>
       <c r="O336" t="inlineStr"/>
       <c r="P336" t="inlineStr">
@@ -36169,10 +35879,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z336" t="inlineStr">
-        <is>
-          <t>582.0</t>
-        </is>
+      <c r="Z336" t="n">
+        <v>582</v>
       </c>
       <c r="AA336" t="inlineStr">
         <is>
@@ -36244,10 +35952,8 @@
           <t>19:36</t>
         </is>
       </c>
-      <c r="N337" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+      <c r="N337" t="n">
+        <v>93</v>
       </c>
       <c r="O337" t="inlineStr"/>
       <c r="P337" t="inlineStr">
@@ -36290,10 +35996,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z337" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
+      <c r="Z337" t="n">
+        <v>53</v>
       </c>
       <c r="AA337" t="inlineStr">
         <is>
@@ -36365,10 +36069,8 @@
           <t>19:51</t>
         </is>
       </c>
-      <c r="N338" t="inlineStr">
-        <is>
-          <t>1137</t>
-        </is>
+      <c r="N338" t="n">
+        <v>1137</v>
       </c>
       <c r="O338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
@@ -36411,10 +36113,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z338" t="inlineStr">
-        <is>
-          <t>252.0</t>
-        </is>
+      <c r="Z338" t="n">
+        <v>252</v>
       </c>
       <c r="AA338" t="inlineStr">
         <is>
@@ -36486,10 +36186,8 @@
           <t>19:45</t>
         </is>
       </c>
-      <c r="N339" t="inlineStr">
-        <is>
-          <t>1148</t>
-        </is>
+      <c r="N339" t="n">
+        <v>1148</v>
       </c>
       <c r="O339" t="inlineStr"/>
       <c r="P339" t="inlineStr">
@@ -36532,10 +36230,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z339" t="inlineStr">
-        <is>
-          <t>596.0</t>
-        </is>
+      <c r="Z339" t="n">
+        <v>596</v>
       </c>
       <c r="AA339" t="inlineStr">
         <is>
@@ -36607,10 +36303,8 @@
           <t>19:50</t>
         </is>
       </c>
-      <c r="N340" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+      <c r="N340" t="n">
+        <v>105</v>
       </c>
       <c r="O340" t="inlineStr"/>
       <c r="P340" t="inlineStr">
@@ -36653,10 +36347,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z340" t="inlineStr">
-        <is>
-          <t>61.0</t>
-        </is>
+      <c r="Z340" t="n">
+        <v>61</v>
       </c>
       <c r="AA340" t="inlineStr">
         <is>
@@ -36728,10 +36420,8 @@
           <t>19:43</t>
         </is>
       </c>
-      <c r="N341" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
+      <c r="N341" t="n">
+        <v>110</v>
       </c>
       <c r="O341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
@@ -36774,10 +36464,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z341" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
+      <c r="Z341" t="n">
+        <v>64</v>
       </c>
       <c r="AA341" t="inlineStr">
         <is>
@@ -36849,10 +36537,8 @@
           <t>19:50</t>
         </is>
       </c>
-      <c r="N342" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
+      <c r="N342" t="n">
+        <v>1217</v>
       </c>
       <c r="O342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
@@ -36895,10 +36581,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z342" t="inlineStr">
-        <is>
-          <t>626.0</t>
-        </is>
+      <c r="Z342" t="n">
+        <v>626</v>
       </c>
       <c r="AA342" t="inlineStr">
         <is>
@@ -36970,10 +36654,8 @@
           <t>19:38</t>
         </is>
       </c>
-      <c r="N343" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
+      <c r="N343" t="n">
+        <v>1224</v>
       </c>
       <c r="O343" t="inlineStr"/>
       <c r="P343" t="inlineStr">
@@ -37016,10 +36698,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z343" t="inlineStr">
-        <is>
-          <t>628.0</t>
-        </is>
+      <c r="Z343" t="n">
+        <v>628</v>
       </c>
       <c r="AA343" t="inlineStr">
         <is>
@@ -37091,10 +36771,8 @@
           <t>19:37</t>
         </is>
       </c>
-      <c r="N344" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
+      <c r="N344" t="n">
+        <v>1236</v>
       </c>
       <c r="O344" t="inlineStr"/>
       <c r="P344" t="inlineStr">
@@ -37137,10 +36815,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z344" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
+      <c r="Z344" t="n">
+        <v>144</v>
       </c>
       <c r="AA344" t="inlineStr">
         <is>
@@ -37212,10 +36888,8 @@
           <t>19:21</t>
         </is>
       </c>
-      <c r="N345" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
+      <c r="N345" t="n">
+        <v>124</v>
       </c>
       <c r="O345" t="inlineStr"/>
       <c r="P345" t="inlineStr">
@@ -37258,10 +36932,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z345" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
+      <c r="Z345" t="n">
+        <v>72</v>
       </c>
       <c r="AA345" t="inlineStr">
         <is>
@@ -37333,10 +37005,8 @@
           <t>17:32</t>
         </is>
       </c>
-      <c r="N346" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
+      <c r="N346" t="n">
+        <v>1261</v>
       </c>
       <c r="O346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
@@ -37379,10 +37049,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z346" t="inlineStr">
-        <is>
-          <t>288.0</t>
-        </is>
+      <c r="Z346" t="n">
+        <v>288</v>
       </c>
       <c r="AA346" t="inlineStr">
         <is>
@@ -37454,10 +37122,8 @@
           <t>19:26</t>
         </is>
       </c>
-      <c r="N347" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
+      <c r="N347" t="n">
+        <v>1305</v>
       </c>
       <c r="O347" t="inlineStr"/>
       <c r="P347" t="inlineStr">
@@ -37500,10 +37166,8 @@
           <t>M35-39</t>
         </is>
       </c>
-      <c r="Z347" t="inlineStr">
-        <is>
-          <t>300.0</t>
-        </is>
+      <c r="Z347" t="n">
+        <v>300</v>
       </c>
       <c r="AA347" t="inlineStr">
         <is>
@@ -37575,10 +37239,8 @@
           <t>20:02</t>
         </is>
       </c>
-      <c r="N348" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
+      <c r="N348" t="n">
+        <v>132</v>
       </c>
       <c r="O348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
@@ -37621,10 +37283,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z348" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
+      <c r="Z348" t="n">
+        <v>79</v>
       </c>
       <c r="AA348" t="inlineStr">
         <is>
@@ -37696,10 +37356,8 @@
           <t>19:48</t>
         </is>
       </c>
-      <c r="N349" t="inlineStr">
-        <is>
-          <t>1362</t>
-        </is>
+      <c r="N349" t="n">
+        <v>1362</v>
       </c>
       <c r="O349" t="inlineStr"/>
       <c r="P349" t="inlineStr">
@@ -37742,10 +37400,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z349" t="inlineStr">
-        <is>
-          <t>688.0</t>
-        </is>
+      <c r="Z349" t="n">
+        <v>688</v>
       </c>
       <c r="AA349" t="inlineStr">
         <is>
@@ -37817,10 +37473,8 @@
           <t>19:50</t>
         </is>
       </c>
-      <c r="N350" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
+      <c r="N350" t="n">
+        <v>138</v>
       </c>
       <c r="O350" t="inlineStr"/>
       <c r="P350" t="inlineStr">
@@ -37863,10 +37517,8 @@
           <t>K20-22</t>
         </is>
       </c>
-      <c r="Z350" t="inlineStr">
-        <is>
-          <t>12.0</t>
-        </is>
+      <c r="Z350" t="n">
+        <v>12</v>
       </c>
       <c r="AA350" t="inlineStr">
         <is>
@@ -37938,10 +37590,8 @@
           <t>20:01</t>
         </is>
       </c>
-      <c r="N351" t="inlineStr">
-        <is>
-          <t>1395</t>
-        </is>
+      <c r="N351" t="n">
+        <v>1395</v>
       </c>
       <c r="O351" t="inlineStr"/>
       <c r="P351" t="inlineStr">
@@ -37984,10 +37634,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z351" t="inlineStr">
-        <is>
-          <t>169.0</t>
-        </is>
+      <c r="Z351" t="n">
+        <v>169</v>
       </c>
       <c r="AA351" t="inlineStr">
         <is>
@@ -38059,10 +37707,8 @@
           <t>19:57</t>
         </is>
       </c>
-      <c r="N352" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
+      <c r="N352" t="n">
+        <v>144</v>
       </c>
       <c r="O352" t="inlineStr"/>
       <c r="P352" t="inlineStr">
@@ -38105,10 +37751,8 @@
           <t>K35-39</t>
         </is>
       </c>
-      <c r="Z352" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
+      <c r="Z352" t="n">
+        <v>28</v>
       </c>
       <c r="AA352" t="inlineStr">
         <is>
@@ -38180,10 +37824,8 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="N353" t="inlineStr">
-        <is>
-          <t>1407</t>
-        </is>
+      <c r="N353" t="n">
+        <v>1407</v>
       </c>
       <c r="O353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
@@ -38226,10 +37868,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z353" t="inlineStr">
-        <is>
-          <t>705.0</t>
-        </is>
+      <c r="Z353" t="n">
+        <v>705</v>
       </c>
       <c r="AA353" t="inlineStr">
         <is>
@@ -38301,10 +37941,8 @@
           <t>20:11</t>
         </is>
       </c>
-      <c r="N354" t="inlineStr">
-        <is>
-          <t>1432</t>
-        </is>
+      <c r="N354" t="n">
+        <v>1432</v>
       </c>
       <c r="O354" t="inlineStr"/>
       <c r="P354" t="inlineStr">
@@ -38347,10 +37985,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z354" t="inlineStr">
-        <is>
-          <t>722.0</t>
-        </is>
+      <c r="Z354" t="n">
+        <v>722</v>
       </c>
       <c r="AA354" t="inlineStr">
         <is>
@@ -38422,10 +38058,8 @@
           <t>20:01</t>
         </is>
       </c>
-      <c r="N355" t="inlineStr">
-        <is>
-          <t>1515</t>
-        </is>
+      <c r="N355" t="n">
+        <v>1515</v>
       </c>
       <c r="O355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
@@ -38468,10 +38102,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z355" t="inlineStr">
-        <is>
-          <t>760.0</t>
-        </is>
+      <c r="Z355" t="n">
+        <v>760</v>
       </c>
       <c r="AA355" t="inlineStr">
         <is>
@@ -38543,10 +38175,8 @@
           <t>20:31</t>
         </is>
       </c>
-      <c r="N356" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
+      <c r="N356" t="n">
+        <v>175</v>
       </c>
       <c r="O356" t="inlineStr"/>
       <c r="P356" t="inlineStr">
@@ -38589,10 +38219,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z356" t="inlineStr">
-        <is>
-          <t>97.0</t>
-        </is>
+      <c r="Z356" t="n">
+        <v>97</v>
       </c>
       <c r="AA356" t="inlineStr">
         <is>
@@ -38664,10 +38292,8 @@
           <t>20:11</t>
         </is>
       </c>
-      <c r="N357" t="inlineStr">
-        <is>
-          <t>1659</t>
-        </is>
+      <c r="N357" t="n">
+        <v>1659</v>
       </c>
       <c r="O357" t="inlineStr"/>
       <c r="P357" t="inlineStr">
@@ -38710,10 +38336,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z357" t="inlineStr">
-        <is>
-          <t>816.0</t>
-        </is>
+      <c r="Z357" t="n">
+        <v>816</v>
       </c>
       <c r="AA357" t="inlineStr">
         <is>
@@ -38785,10 +38409,8 @@
           <t>20:38</t>
         </is>
       </c>
-      <c r="N358" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="N358" t="n">
+        <v>192</v>
       </c>
       <c r="O358" t="inlineStr"/>
       <c r="P358" t="inlineStr">
@@ -38831,10 +38453,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z358" t="inlineStr">
-        <is>
-          <t>111.0</t>
-        </is>
+      <c r="Z358" t="n">
+        <v>111</v>
       </c>
       <c r="AA358" t="inlineStr">
         <is>
@@ -38906,10 +38526,8 @@
           <t>20:44</t>
         </is>
       </c>
-      <c r="N359" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
+      <c r="N359" t="n">
+        <v>194</v>
       </c>
       <c r="O359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
@@ -38952,10 +38570,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z359" t="inlineStr">
-        <is>
-          <t>112.0</t>
-        </is>
+      <c r="Z359" t="n">
+        <v>112</v>
       </c>
       <c r="AA359" t="inlineStr">
         <is>
@@ -39027,10 +38643,8 @@
           <t>20:51</t>
         </is>
       </c>
-      <c r="N360" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
+      <c r="N360" t="n">
+        <v>203</v>
       </c>
       <c r="O360" t="inlineStr"/>
       <c r="P360" t="inlineStr">
@@ -39073,10 +38687,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z360" t="inlineStr">
-        <is>
-          <t>120.0</t>
-        </is>
+      <c r="Z360" t="n">
+        <v>120</v>
       </c>
       <c r="AA360" t="inlineStr">
         <is>
@@ -39148,10 +38760,8 @@
           <t>20:58</t>
         </is>
       </c>
-      <c r="N361" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
+      <c r="N361" t="n">
+        <v>210</v>
       </c>
       <c r="O361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
@@ -39194,10 +38804,8 @@
           <t>K35-39</t>
         </is>
       </c>
-      <c r="Z361" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
+      <c r="Z361" t="n">
+        <v>40</v>
       </c>
       <c r="AA361" t="inlineStr">
         <is>
@@ -39269,10 +38877,8 @@
           <t>20:34</t>
         </is>
       </c>
-      <c r="N362" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
+      <c r="N362" t="n">
+        <v>228</v>
       </c>
       <c r="O362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
@@ -39315,10 +38921,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z362" t="inlineStr">
-        <is>
-          <t>136.0</t>
-        </is>
+      <c r="Z362" t="n">
+        <v>136</v>
       </c>
       <c r="AA362" t="inlineStr">
         <is>
@@ -39390,10 +38994,8 @@
           <t>20:00</t>
         </is>
       </c>
-      <c r="N363" t="inlineStr">
-        <is>
-          <t>1787</t>
-        </is>
+      <c r="N363" t="n">
+        <v>1787</v>
       </c>
       <c r="O363" t="inlineStr"/>
       <c r="P363" t="inlineStr">
@@ -39436,10 +39038,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z363" t="inlineStr">
-        <is>
-          <t>873.0</t>
-        </is>
+      <c r="Z363" t="n">
+        <v>873</v>
       </c>
       <c r="AA363" t="inlineStr">
         <is>
@@ -39511,10 +39111,8 @@
           <t>20:54</t>
         </is>
       </c>
-      <c r="N364" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
+      <c r="N364" t="n">
+        <v>238</v>
       </c>
       <c r="O364" t="inlineStr"/>
       <c r="P364" t="inlineStr">
@@ -39557,10 +39155,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z364" t="inlineStr">
-        <is>
-          <t>143.0</t>
-        </is>
+      <c r="Z364" t="n">
+        <v>143</v>
       </c>
       <c r="AA364" t="inlineStr">
         <is>
@@ -39632,10 +39228,8 @@
           <t>20:26</t>
         </is>
       </c>
-      <c r="N365" t="inlineStr">
-        <is>
-          <t>1817</t>
-        </is>
+      <c r="N365" t="n">
+        <v>1817</v>
       </c>
       <c r="O365" t="inlineStr"/>
       <c r="P365" t="inlineStr">
@@ -39678,10 +39272,8 @@
           <t>M50-54</t>
         </is>
       </c>
-      <c r="Z365" t="inlineStr">
-        <is>
-          <t>52.0</t>
-        </is>
+      <c r="Z365" t="n">
+        <v>52</v>
       </c>
       <c r="AA365" t="inlineStr">
         <is>
@@ -39753,10 +39345,8 @@
           <t>21:03</t>
         </is>
       </c>
-      <c r="N366" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="N366" t="n">
+        <v>1826</v>
       </c>
       <c r="O366" t="inlineStr"/>
       <c r="P366" t="inlineStr">
@@ -39799,10 +39389,8 @@
           <t>M55-59</t>
         </is>
       </c>
-      <c r="Z366" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
+      <c r="Z366" t="n">
+        <v>33</v>
       </c>
       <c r="AA366" t="inlineStr">
         <is>
@@ -39874,10 +39462,8 @@
           <t>20:37</t>
         </is>
       </c>
-      <c r="N367" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
+      <c r="N367" t="n">
+        <v>262</v>
       </c>
       <c r="O367" t="inlineStr"/>
       <c r="P367" t="inlineStr">
@@ -39920,10 +39506,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z367" t="inlineStr">
-        <is>
-          <t>157.0</t>
-        </is>
+      <c r="Z367" t="n">
+        <v>157</v>
       </c>
       <c r="AA367" t="inlineStr">
         <is>
@@ -39995,10 +39579,8 @@
           <t>21:07</t>
         </is>
       </c>
-      <c r="N368" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
+      <c r="N368" t="n">
+        <v>264</v>
       </c>
       <c r="O368" t="inlineStr"/>
       <c r="P368" t="inlineStr">
@@ -40041,10 +39623,8 @@
           <t>K18-19</t>
         </is>
       </c>
-      <c r="Z368" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="Z368" t="n">
+        <v>5</v>
       </c>
       <c r="AA368" t="inlineStr">
         <is>
@@ -40116,10 +39696,8 @@
           <t>21:17</t>
         </is>
       </c>
-      <c r="N369" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
+      <c r="N369" t="n">
+        <v>297</v>
       </c>
       <c r="O369" t="inlineStr"/>
       <c r="P369" t="inlineStr">
@@ -40162,10 +39740,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z369" t="inlineStr">
-        <is>
-          <t>172.0</t>
-        </is>
+      <c r="Z369" t="n">
+        <v>172</v>
       </c>
       <c r="AA369" t="inlineStr">
         <is>
@@ -40237,10 +39813,8 @@
           <t>21:14</t>
         </is>
       </c>
-      <c r="N370" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
+      <c r="N370" t="n">
+        <v>2049</v>
       </c>
       <c r="O370" t="inlineStr"/>
       <c r="P370" t="inlineStr">
@@ -40283,10 +39857,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z370" t="inlineStr">
-        <is>
-          <t>967.0</t>
-        </is>
+      <c r="Z370" t="n">
+        <v>967</v>
       </c>
       <c r="AA370" t="inlineStr">
         <is>
@@ -40358,10 +39930,8 @@
           <t>21:45</t>
         </is>
       </c>
-      <c r="N371" t="inlineStr">
-        <is>
-          <t>2145</t>
-        </is>
+      <c r="N371" t="n">
+        <v>2145</v>
       </c>
       <c r="O371" t="inlineStr"/>
       <c r="P371" t="inlineStr">
@@ -40404,10 +39974,8 @@
           <t>M50-54</t>
         </is>
       </c>
-      <c r="Z371" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
+      <c r="Z371" t="n">
+        <v>78</v>
       </c>
       <c r="AA371" t="inlineStr">
         <is>
@@ -40479,10 +40047,8 @@
           <t>22:15</t>
         </is>
       </c>
-      <c r="N372" t="inlineStr">
-        <is>
-          <t>2175</t>
-        </is>
+      <c r="N372" t="n">
+        <v>2175</v>
       </c>
       <c r="O372" t="inlineStr"/>
       <c r="P372" t="inlineStr">
@@ -40525,10 +40091,8 @@
           <t>M60-64</t>
         </is>
       </c>
-      <c r="Z372" t="inlineStr">
-        <is>
-          <t>16.0</t>
-        </is>
+      <c r="Z372" t="n">
+        <v>16</v>
       </c>
       <c r="AA372" t="inlineStr">
         <is>
@@ -40600,10 +40164,8 @@
           <t>22:35</t>
         </is>
       </c>
-      <c r="N373" t="inlineStr">
-        <is>
-          <t>391</t>
-        </is>
+      <c r="N373" t="n">
+        <v>391</v>
       </c>
       <c r="O373" t="inlineStr"/>
       <c r="P373" t="inlineStr">
@@ -40646,10 +40208,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z373" t="inlineStr">
-        <is>
-          <t>229.0</t>
-        </is>
+      <c r="Z373" t="n">
+        <v>229</v>
       </c>
       <c r="AA373" t="inlineStr">
         <is>
@@ -40721,10 +40281,8 @@
           <t>22:21</t>
         </is>
       </c>
-      <c r="N374" t="inlineStr">
-        <is>
-          <t>2305</t>
-        </is>
+      <c r="N374" t="n">
+        <v>2305</v>
       </c>
       <c r="O374" t="inlineStr"/>
       <c r="P374" t="inlineStr">
@@ -40767,10 +40325,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z374" t="inlineStr">
-        <is>
-          <t>1055.0</t>
-        </is>
+      <c r="Z374" t="n">
+        <v>1055</v>
       </c>
       <c r="AA374" t="inlineStr">
         <is>
@@ -40842,10 +40398,8 @@
           <t>22:20</t>
         </is>
       </c>
-      <c r="N375" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
+      <c r="N375" t="n">
+        <v>462</v>
       </c>
       <c r="O375" t="inlineStr"/>
       <c r="P375" t="inlineStr">
@@ -40888,10 +40442,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z375" t="inlineStr">
-        <is>
-          <t>261.0</t>
-        </is>
+      <c r="Z375" t="n">
+        <v>261</v>
       </c>
       <c r="AA375" t="inlineStr">
         <is>
@@ -40963,10 +40515,8 @@
           <t>23:23</t>
         </is>
       </c>
-      <c r="N376" t="inlineStr">
-        <is>
-          <t>464</t>
-        </is>
+      <c r="N376" t="n">
+        <v>464</v>
       </c>
       <c r="O376" t="inlineStr"/>
       <c r="P376" t="inlineStr">
@@ -41009,10 +40559,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z376" t="inlineStr">
-        <is>
-          <t>263.0</t>
-        </is>
+      <c r="Z376" t="n">
+        <v>263</v>
       </c>
       <c r="AA376" t="inlineStr">
         <is>
@@ -41084,10 +40632,8 @@
           <t>22:53</t>
         </is>
       </c>
-      <c r="N377" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
+      <c r="N377" t="n">
+        <v>3040</v>
       </c>
       <c r="O377" t="inlineStr"/>
       <c r="P377" t="inlineStr">
@@ -41201,10 +40747,8 @@
           <t>23:28</t>
         </is>
       </c>
-      <c r="N378" t="inlineStr">
-        <is>
-          <t>2543</t>
-        </is>
+      <c r="N378" t="n">
+        <v>2543</v>
       </c>
       <c r="O378" t="inlineStr"/>
       <c r="P378" t="inlineStr">
@@ -41247,10 +40791,8 @@
           <t>M60-64</t>
         </is>
       </c>
-      <c r="Z378" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
+      <c r="Z378" t="n">
+        <v>28</v>
       </c>
       <c r="AA378" t="inlineStr">
         <is>
@@ -41322,10 +40864,8 @@
           <t>24:16</t>
         </is>
       </c>
-      <c r="N379" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
+      <c r="N379" t="n">
+        <v>577</v>
       </c>
       <c r="O379" t="inlineStr"/>
       <c r="P379" t="inlineStr">
@@ -41368,10 +40908,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z379" t="inlineStr">
-        <is>
-          <t>315.0</t>
-        </is>
+      <c r="Z379" t="n">
+        <v>315</v>
       </c>
       <c r="AA379" t="inlineStr">
         <is>
@@ -41443,10 +40981,8 @@
           <t>24:18</t>
         </is>
       </c>
-      <c r="N380" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
+      <c r="N380" t="n">
+        <v>599</v>
       </c>
       <c r="O380" t="inlineStr"/>
       <c r="P380" t="inlineStr">
@@ -41489,10 +41025,8 @@
           <t>K40-44</t>
         </is>
       </c>
-      <c r="Z380" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
+      <c r="Z380" t="n">
+        <v>62</v>
       </c>
       <c r="AA380" t="inlineStr">
         <is>
@@ -41564,10 +41098,8 @@
           <t>27:43</t>
         </is>
       </c>
-      <c r="N381" t="inlineStr">
-        <is>
-          <t>979</t>
-        </is>
+      <c r="N381" t="n">
+        <v>979</v>
       </c>
       <c r="O381" t="inlineStr"/>
       <c r="P381" t="inlineStr">
@@ -41610,10 +41142,8 @@
           <t>K23-34</t>
         </is>
       </c>
-      <c r="Z381" t="inlineStr">
-        <is>
-          <t>493.0</t>
-        </is>
+      <c r="Z381" t="n">
+        <v>493</v>
       </c>
       <c r="AA381" t="inlineStr">
         <is>
@@ -41632,6 +41162,115 @@
       </c>
       <c r="AD381" t="inlineStr"/>
       <c r="AE381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>15</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>NN Marathon Rotterdam</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Maraton</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>MSR</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Kristian Fr?yen</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr"/>
+      <c r="H382" t="inlineStr"/>
+      <c r="I382" t="inlineStr"/>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>2:35:16</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>2:35:16</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>BIB 21457. Guntid 2:35:27. Klasseplass 97. NC/klasse MSR.</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>NN Marathon Rotterdam manuell registrering fra tekst</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>manual-2026-04-12-rotterdam-marathon</t>
+        </is>
+      </c>
+      <c r="R382" t="n">
+        <v>146</v>
+      </c>
+      <c r="S382" t="inlineStr"/>
+      <c r="T382" t="inlineStr"/>
+      <c r="U382" t="inlineStr"/>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>Manuell registrering</t>
+        </is>
+      </c>
+      <c r="W382" t="inlineStr"/>
+      <c r="X382" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y382" t="inlineStr">
+        <is>
+          <t>MSR</t>
+        </is>
+      </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AA382" t="inlineStr">
+        <is>
+          <t>1:14:53</t>
+        </is>
+      </c>
+      <c r="AB382" t="inlineStr"/>
+      <c r="AC382" t="inlineStr"/>
+      <c r="AD382" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE382" t="inlineStr">
+        <is>
+          <t>Maraton</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/arbeidsfiler/weekly_results_2026.xlsx
+++ b/data/arbeidsfiler/weekly_results_2026.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE382"/>
+  <dimension ref="A1:AE385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41277,6 +41277,365 @@
       </c>
       <c r="AD382" t="inlineStr"/>
       <c r="AE382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>15</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Drammen10K</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>K23-34</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Kari Renslo</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr"/>
+      <c r="I383" t="inlineStr"/>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>42:38</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>42:38</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="N383" t="n">
+        <v>2244</v>
+      </c>
+      <c r="O383" t="inlineStr"/>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>https://live.ultimate.dk/desktop/front/index.php?eventid=7069&amp;ignoreuseragent=true&amp;pid=3644</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>drammen-manual-kari-renslo-2026</t>
+        </is>
+      </c>
+      <c r="R383" t="n">
+        <v>2244</v>
+      </c>
+      <c r="S383" t="inlineStr"/>
+      <c r="T383" t="inlineStr"/>
+      <c r="U383" t="inlineStr"/>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>Drammen manual add 2026</t>
+        </is>
+      </c>
+      <c r="W383" t="inlineStr"/>
+      <c r="X383" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="Y383" t="inlineStr">
+        <is>
+          <t>K23-34</t>
+        </is>
+      </c>
+      <c r="Z383" t="n">
+        <v>161</v>
+      </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="AB383" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AC383" t="inlineStr">
+        <is>
+          <t>+2:22</t>
+        </is>
+      </c>
+      <c r="AD383" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="AE383" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>15</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Drammen10K</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>M40-44</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Thomas Nordb? Berg</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr"/>
+      <c r="I384" t="inlineStr"/>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>36:35</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>36:35</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>689</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr"/>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>https://live.ultimate.dk/desktop/front/index.php?eventid=7069&amp;ignoreuseragent=true&amp;pid=1780</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>drammen-manual-add-2026</t>
+        </is>
+      </c>
+      <c r="R384" t="n">
+        <v>689</v>
+      </c>
+      <c r="S384" t="inlineStr"/>
+      <c r="T384" t="inlineStr"/>
+      <c r="U384" t="inlineStr"/>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>Drammen manual add 2026</t>
+        </is>
+      </c>
+      <c r="W384" t="inlineStr"/>
+      <c r="X384" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y384" t="inlineStr">
+        <is>
+          <t>M40-44</t>
+        </is>
+      </c>
+      <c r="Z384" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AB384" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AC384" t="inlineStr">
+        <is>
+          <t>-0:25</t>
+        </is>
+      </c>
+      <c r="AD384" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE384" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>15</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Drammen10K</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>M55-59</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Arvin Patel</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr"/>
+      <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>40:26</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>40:26</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>1731</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr"/>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>https://live.ultimate.dk/desktop/front/index.php?eventid=7069&amp;ignoreuseragent=true&amp;pid=2734</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>drammen-manual-add-2026</t>
+        </is>
+      </c>
+      <c r="R385" t="n">
+        <v>1731</v>
+      </c>
+      <c r="S385" t="inlineStr"/>
+      <c r="T385" t="inlineStr"/>
+      <c r="U385" t="inlineStr"/>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>Drammen manual add 2026</t>
+        </is>
+      </c>
+      <c r="W385" t="inlineStr"/>
+      <c r="X385" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y385" t="inlineStr">
+        <is>
+          <t>M55-59</t>
+        </is>
+      </c>
+      <c r="Z385" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA385" t="inlineStr">
+        <is>
+          <t>20:11</t>
+        </is>
+      </c>
+      <c r="AB385" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AC385" t="inlineStr">
+        <is>
+          <t>+0:04</t>
+        </is>
+      </c>
+      <c r="AD385" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE385" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/arbeidsfiler/weekly_results_2026.xlsx
+++ b/data/arbeidsfiler/weekly_results_2026.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE385"/>
+  <dimension ref="A1:AE392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41421,7 +41421,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Thomas Nordb? Berg</t>
+          <t>Thomas Nordbø Berg</t>
         </is>
       </c>
       <c r="G384" t="inlineStr"/>
@@ -41447,10 +41447,8 @@
           <t>18:30</t>
         </is>
       </c>
-      <c r="N384" t="inlineStr">
-        <is>
-          <t>689</t>
-        </is>
+      <c r="N384" t="n">
+        <v>689</v>
       </c>
       <c r="O384" t="inlineStr"/>
       <c r="P384" t="inlineStr">
@@ -41485,10 +41483,8 @@
           <t>M40-44</t>
         </is>
       </c>
-      <c r="Z384" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
+      <c r="Z384" t="n">
+        <v>60</v>
       </c>
       <c r="AA384" t="inlineStr">
         <is>
@@ -41568,10 +41564,8 @@
           <t>20:11</t>
         </is>
       </c>
-      <c r="N385" t="inlineStr">
-        <is>
-          <t>1731</t>
-        </is>
+      <c r="N385" t="n">
+        <v>1731</v>
       </c>
       <c r="O385" t="inlineStr"/>
       <c r="P385" t="inlineStr">
@@ -41606,10 +41600,8 @@
           <t>M55-59</t>
         </is>
       </c>
-      <c r="Z385" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="Z385" t="n">
+        <v>22</v>
       </c>
       <c r="AA385" t="inlineStr">
         <is>
@@ -41632,6 +41624,829 @@
         </is>
       </c>
       <c r="AE385" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B386" t="n">
+        <v>15</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Drammen10K</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>M23-34</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Sigve Varslott Aalmo</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr"/>
+      <c r="I386" t="inlineStr"/>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>37:58</t>
+        </is>
+      </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>37:58</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="N386" t="n">
+        <v>982</v>
+      </c>
+      <c r="O386" t="inlineStr"/>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>https://live.ultimate.dk/desktop/front/index.php?eventid=7069&amp;ignoreuseragent=true&amp;pid=1623</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>drammen-manual-add-2026</t>
+        </is>
+      </c>
+      <c r="R386" t="n">
+        <v>982</v>
+      </c>
+      <c r="S386" t="inlineStr"/>
+      <c r="T386" t="inlineStr"/>
+      <c r="U386" t="inlineStr"/>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>Drammen manual add 2026</t>
+        </is>
+      </c>
+      <c r="W386" t="inlineStr"/>
+      <c r="X386" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y386" t="inlineStr">
+        <is>
+          <t>M23-34</t>
+        </is>
+      </c>
+      <c r="Z386" t="n">
+        <v>491</v>
+      </c>
+      <c r="AA386" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AB386" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC386" t="inlineStr">
+        <is>
+          <t>+0:02</t>
+        </is>
+      </c>
+      <c r="AD386" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE386" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>15</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Drammen10K</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>M23-34</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Martin Kvam</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" t="inlineStr"/>
+      <c r="I387" t="inlineStr"/>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>37:57</t>
+        </is>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>37:57</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="N387" t="n">
+        <v>980</v>
+      </c>
+      <c r="O387" t="inlineStr"/>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>https://live.ultimate.dk/desktop/front/index.php?eventid=7069&amp;ignoreuseragent=true&amp;pid=1617</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>drammen-manual-add-2026</t>
+        </is>
+      </c>
+      <c r="R387" t="n">
+        <v>980</v>
+      </c>
+      <c r="S387" t="inlineStr"/>
+      <c r="T387" t="inlineStr"/>
+      <c r="U387" t="inlineStr"/>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>Drammen manual add 2026</t>
+        </is>
+      </c>
+      <c r="W387" t="inlineStr"/>
+      <c r="X387" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y387" t="inlineStr">
+        <is>
+          <t>M23-34</t>
+        </is>
+      </c>
+      <c r="Z387" t="n">
+        <v>490</v>
+      </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="AB387" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="AC387" t="inlineStr">
+        <is>
+          <t>-0:33</t>
+        </is>
+      </c>
+      <c r="AD387" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE387" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B388" t="n">
+        <v>15</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Drammen10K</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>M35-39</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Eivind Bækkedal</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr"/>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>36:33</t>
+        </is>
+      </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>36:33</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="N388" t="n">
+        <v>683</v>
+      </c>
+      <c r="O388" t="inlineStr"/>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>https://live.ultimate.dk/desktop/front/index.php?eventid=7069&amp;ignoreuseragent=true&amp;pid=3179</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>drammen-manual-add-2026</t>
+        </is>
+      </c>
+      <c r="R388" t="n">
+        <v>683</v>
+      </c>
+      <c r="S388" t="inlineStr"/>
+      <c r="T388" t="inlineStr"/>
+      <c r="U388" t="inlineStr"/>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>Drammen manual add 2026</t>
+        </is>
+      </c>
+      <c r="W388" t="inlineStr"/>
+      <c r="X388" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y388" t="inlineStr">
+        <is>
+          <t>M35-39</t>
+        </is>
+      </c>
+      <c r="Z388" t="n">
+        <v>141</v>
+      </c>
+      <c r="AA388" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AB388" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC388" t="inlineStr">
+        <is>
+          <t>-1:09</t>
+        </is>
+      </c>
+      <c r="AD388" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE388" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B389" t="n">
+        <v>15</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Drammen10K</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>M23-34</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Mikkel Trøstheim</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr"/>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>36:07</t>
+        </is>
+      </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>36:07</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="N389" t="n">
+        <v>586</v>
+      </c>
+      <c r="O389" t="inlineStr"/>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>https://live.ultimate.dk/desktop/front/index.php?eventid=7069&amp;ignoreuseragent=true&amp;pid=1287</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>drammen-manual-add-2026</t>
+        </is>
+      </c>
+      <c r="R389" t="n">
+        <v>586</v>
+      </c>
+      <c r="S389" t="inlineStr"/>
+      <c r="T389" t="inlineStr"/>
+      <c r="U389" t="inlineStr"/>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>Drammen manual add 2026</t>
+        </is>
+      </c>
+      <c r="W389" t="inlineStr"/>
+      <c r="X389" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y389" t="inlineStr">
+        <is>
+          <t>M23-34</t>
+        </is>
+      </c>
+      <c r="Z389" t="n">
+        <v>305</v>
+      </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AB389" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC389" t="inlineStr">
+        <is>
+          <t>-0:21</t>
+        </is>
+      </c>
+      <c r="AD389" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE389" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>15</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Drammen10K</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>M23-34</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Jacob Nitter</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr"/>
+      <c r="I390" t="inlineStr"/>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>35:53</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>35:53</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="N390" t="n">
+        <v>552</v>
+      </c>
+      <c r="O390" t="inlineStr"/>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>https://live.ultimate.dk/desktop/front/index.php?eventid=7069&amp;ignoreuseragent=true&amp;pid=1707</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>drammen-manual-add-2026</t>
+        </is>
+      </c>
+      <c r="R390" t="n">
+        <v>552</v>
+      </c>
+      <c r="S390" t="inlineStr"/>
+      <c r="T390" t="inlineStr"/>
+      <c r="U390" t="inlineStr"/>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>Drammen manual add 2026</t>
+        </is>
+      </c>
+      <c r="W390" t="inlineStr"/>
+      <c r="X390" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y390" t="inlineStr">
+        <is>
+          <t>M23-34</t>
+        </is>
+      </c>
+      <c r="Z390" t="n">
+        <v>291</v>
+      </c>
+      <c r="AA390" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="AB390" t="inlineStr">
+        <is>
+          <t>17:52</t>
+        </is>
+      </c>
+      <c r="AC390" t="inlineStr">
+        <is>
+          <t>-0:09</t>
+        </is>
+      </c>
+      <c r="AD390" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE390" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>15</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Drammen10K</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>M35-39</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Ole-Henrik Kabbe</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr"/>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>31:56</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>31:56</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="N391" t="n">
+        <v>81</v>
+      </c>
+      <c r="O391" t="inlineStr"/>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>https://live.ultimate.dk/desktop/front/index.php?eventid=7069&amp;ignoreuseragent=true&amp;pid=1040</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>drammen-manual-add-2026</t>
+        </is>
+      </c>
+      <c r="R391" t="n">
+        <v>81</v>
+      </c>
+      <c r="S391" t="inlineStr"/>
+      <c r="T391" t="inlineStr"/>
+      <c r="U391" t="inlineStr"/>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>Drammen manual add 2026</t>
+        </is>
+      </c>
+      <c r="W391" t="inlineStr"/>
+      <c r="X391" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y391" t="inlineStr">
+        <is>
+          <t>M35-39</t>
+        </is>
+      </c>
+      <c r="Z391" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA391" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AB391" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AC391" t="inlineStr">
+        <is>
+          <t>+0:32</t>
+        </is>
+      </c>
+      <c r="AD391" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE391" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>15</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Drammen10K</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>10 km</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>M23-34</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Henrik Håkonsen</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr"/>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>38:45</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>38:45</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>1180</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr"/>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>https://live.ultimate.dk/desktop/front/index.php?eventid=7069&amp;ignoreuseragent=true&amp;pid=1140</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>drammen-manual-add-2026</t>
+        </is>
+      </c>
+      <c r="R392" t="n">
+        <v>1180</v>
+      </c>
+      <c r="S392" t="inlineStr"/>
+      <c r="T392" t="inlineStr"/>
+      <c r="U392" t="inlineStr"/>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>Drammen manual add 2026</t>
+        </is>
+      </c>
+      <c r="W392" t="inlineStr"/>
+      <c r="X392" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y392" t="inlineStr">
+        <is>
+          <t>M23-34</t>
+        </is>
+      </c>
+      <c r="Z392" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="AA392" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AB392" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AC392" t="inlineStr">
+        <is>
+          <t>-0:11</t>
+        </is>
+      </c>
+      <c r="AD392" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE392" t="inlineStr">
         <is>
           <t>10 km</t>
         </is>

--- a/data/arbeidsfiler/weekly_results_2026.xlsx
+++ b/data/arbeidsfiler/weekly_results_2026.xlsx
@@ -27409,12 +27409,12 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="N264" t="n">
@@ -27466,19 +27466,11 @@
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>19:28</t>
-        </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>-7:56</t>
-        </is>
-      </c>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr"/>
+      <c r="AC264" t="inlineStr"/>
       <c r="AD264" t="inlineStr"/>
       <c r="AE264" t="inlineStr"/>
     </row>
@@ -42383,10 +42375,8 @@
           <t>19:28</t>
         </is>
       </c>
-      <c r="N392" t="inlineStr">
-        <is>
-          <t>1180</t>
-        </is>
+      <c r="N392" t="n">
+        <v>1180</v>
       </c>
       <c r="O392" t="inlineStr"/>
       <c r="P392" t="inlineStr">
@@ -42421,10 +42411,8 @@
           <t>M23-34</t>
         </is>
       </c>
-      <c r="Z392" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
+      <c r="Z392" t="n">
+        <v>568</v>
       </c>
       <c r="AA392" t="inlineStr">
         <is>

--- a/data/arbeidsfiler/weekly_results_2026.xlsx
+++ b/data/arbeidsfiler/weekly_results_2026.xlsx
@@ -27409,12 +27409,12 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="N264" t="n">
@@ -27466,7 +27466,7 @@
       </c>
       <c r="AA264" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AB264" t="inlineStr"/>

--- a/data/arbeidsfiler/weekly_results_2026.xlsx
+++ b/data/arbeidsfiler/weekly_results_2026.xlsx
@@ -28345,10 +28345,16 @@
           <t>16:18</t>
         </is>
       </c>
-      <c r="N272" t="n">
-        <v>4</v>
-      </c>
-      <c r="O272" t="inlineStr"/>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>3. plass totalt kvinner.</t>
+        </is>
+      </c>
       <c r="P272" t="inlineStr">
         <is>
           <t>https://live.ultimate.dk/desktop/front/index.php?eventid=7069&amp;ignoreuseragent=true&amp;pid=7009</t>
@@ -30913,8 +30919,10 @@
           <t>16:55</t>
         </is>
       </c>
-      <c r="N294" t="n">
-        <v>14</v>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
       </c>
       <c r="O294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
@@ -31147,8 +31155,10 @@
           <t>17:19</t>
         </is>
       </c>
-      <c r="N296" t="n">
-        <v>17</v>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="O296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
@@ -31264,8 +31274,10 @@
           <t>17:22</t>
         </is>
       </c>
-      <c r="N297" t="n">
-        <v>18</v>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="O297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
@@ -31498,8 +31510,10 @@
           <t>16:37</t>
         </is>
       </c>
-      <c r="N299" t="n">
-        <v>20</v>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="O299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
@@ -31966,8 +31980,10 @@
           <t>17:22</t>
         </is>
       </c>
-      <c r="N303" t="n">
-        <v>23</v>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="O303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
@@ -32083,8 +32099,10 @@
           <t>17:22</t>
         </is>
       </c>
-      <c r="N304" t="n">
-        <v>24</v>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="O304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
@@ -32785,8 +32803,10 @@
           <t>17:58</t>
         </is>
       </c>
-      <c r="N310" t="n">
-        <v>32</v>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
@@ -33838,8 +33858,10 @@
           <t>18:40</t>
         </is>
       </c>
-      <c r="N319" t="n">
-        <v>46</v>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="O319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
@@ -35006,8 +35028,10 @@
           <t>19:10</t>
         </is>
       </c>
-      <c r="N329" t="n">
-        <v>66</v>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
       </c>
       <c r="O329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
@@ -35123,8 +35147,10 @@
           <t>19:11</t>
         </is>
       </c>
-      <c r="N330" t="n">
-        <v>67</v>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
       </c>
       <c r="O330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
@@ -35240,8 +35266,10 @@
           <t>18:53</t>
         </is>
       </c>
-      <c r="N331" t="n">
-        <v>74</v>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
       </c>
       <c r="O331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
@@ -35474,8 +35502,10 @@
           <t>18:58</t>
         </is>
       </c>
-      <c r="N333" t="n">
-        <v>81</v>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
       <c r="O333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
@@ -35591,8 +35621,10 @@
           <t>19:09</t>
         </is>
       </c>
-      <c r="N334" t="n">
-        <v>84</v>
+      <c r="N334" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
       </c>
       <c r="O334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
@@ -36059,8 +36091,10 @@
           <t>19:36</t>
         </is>
       </c>
-      <c r="N338" t="n">
-        <v>93</v>
+      <c r="N338" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
       </c>
       <c r="O338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
@@ -36410,8 +36444,10 @@
           <t>19:50</t>
         </is>
       </c>
-      <c r="N341" t="n">
-        <v>105</v>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
       </c>
       <c r="O341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
@@ -36527,8 +36563,10 @@
           <t>19:43</t>
         </is>
       </c>
-      <c r="N342" t="n">
-        <v>110</v>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
       </c>
       <c r="O342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
@@ -36995,8 +37033,10 @@
           <t>19:21</t>
         </is>
       </c>
-      <c r="N346" t="n">
-        <v>124</v>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
       </c>
       <c r="O346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
@@ -37346,8 +37386,10 @@
           <t>20:02</t>
         </is>
       </c>
-      <c r="N349" t="n">
-        <v>132</v>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
       </c>
       <c r="O349" t="inlineStr"/>
       <c r="P349" t="inlineStr">
@@ -37580,8 +37622,10 @@
           <t>19:50</t>
         </is>
       </c>
-      <c r="N351" t="n">
-        <v>138</v>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
       </c>
       <c r="O351" t="inlineStr"/>
       <c r="P351" t="inlineStr">
@@ -37814,8 +37858,10 @@
           <t>19:57</t>
         </is>
       </c>
-      <c r="N353" t="n">
-        <v>144</v>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
       </c>
       <c r="O353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
@@ -38282,8 +38328,10 @@
           <t>20:31</t>
         </is>
       </c>
-      <c r="N357" t="n">
-        <v>175</v>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
       </c>
       <c r="O357" t="inlineStr"/>
       <c r="P357" t="inlineStr">
@@ -38516,8 +38564,10 @@
           <t>20:38</t>
         </is>
       </c>
-      <c r="N359" t="n">
-        <v>192</v>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
       </c>
       <c r="O359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
@@ -38633,8 +38683,10 @@
           <t>20:44</t>
         </is>
       </c>
-      <c r="N360" t="n">
-        <v>194</v>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
       <c r="O360" t="inlineStr"/>
       <c r="P360" t="inlineStr">
@@ -38750,8 +38802,10 @@
           <t>20:51</t>
         </is>
       </c>
-      <c r="N361" t="n">
-        <v>203</v>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
       </c>
       <c r="O361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
@@ -38867,8 +38921,10 @@
           <t>20:58</t>
         </is>
       </c>
-      <c r="N362" t="n">
-        <v>210</v>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
       </c>
       <c r="O362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
@@ -38984,8 +39040,10 @@
           <t>20:34</t>
         </is>
       </c>
-      <c r="N363" t="n">
-        <v>228</v>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
       </c>
       <c r="O363" t="inlineStr"/>
       <c r="P363" t="inlineStr">
@@ -39218,8 +39276,10 @@
           <t>20:54</t>
         </is>
       </c>
-      <c r="N365" t="n">
-        <v>238</v>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
       </c>
       <c r="O365" t="inlineStr"/>
       <c r="P365" t="inlineStr">
@@ -39569,8 +39629,10 @@
           <t>20:37</t>
         </is>
       </c>
-      <c r="N368" t="n">
-        <v>262</v>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
       </c>
       <c r="O368" t="inlineStr"/>
       <c r="P368" t="inlineStr">
@@ -39686,8 +39748,10 @@
           <t>21:07</t>
         </is>
       </c>
-      <c r="N369" t="n">
-        <v>264</v>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
       </c>
       <c r="O369" t="inlineStr"/>
       <c r="P369" t="inlineStr">
@@ -39803,8 +39867,10 @@
           <t>21:17</t>
         </is>
       </c>
-      <c r="N370" t="n">
-        <v>297</v>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
       </c>
       <c r="O370" t="inlineStr"/>
       <c r="P370" t="inlineStr">
@@ -40271,8 +40337,10 @@
           <t>22:35</t>
         </is>
       </c>
-      <c r="N374" t="n">
-        <v>391</v>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
       </c>
       <c r="O374" t="inlineStr"/>
       <c r="P374" t="inlineStr">
@@ -40505,8 +40573,10 @@
           <t>22:20</t>
         </is>
       </c>
-      <c r="N376" t="n">
-        <v>462</v>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>459</t>
+        </is>
       </c>
       <c r="O376" t="inlineStr"/>
       <c r="P376" t="inlineStr">
@@ -40622,8 +40692,10 @@
           <t>23:23</t>
         </is>
       </c>
-      <c r="N377" t="n">
-        <v>464</v>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
       </c>
       <c r="O377" t="inlineStr"/>
       <c r="P377" t="inlineStr">
@@ -40971,8 +41043,10 @@
           <t>24:16</t>
         </is>
       </c>
-      <c r="N380" t="n">
-        <v>577</v>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
       </c>
       <c r="O380" t="inlineStr"/>
       <c r="P380" t="inlineStr">
@@ -41088,8 +41162,10 @@
           <t>24:18</t>
         </is>
       </c>
-      <c r="N381" t="n">
-        <v>599</v>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
       </c>
       <c r="O381" t="inlineStr"/>
       <c r="P381" t="inlineStr">
@@ -41205,8 +41281,10 @@
           <t>27:43</t>
         </is>
       </c>
-      <c r="N382" t="n">
-        <v>979</v>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
       </c>
       <c r="O382" t="inlineStr"/>
       <c r="P382" t="inlineStr">
@@ -41322,8 +41400,10 @@
           <t>20:08</t>
         </is>
       </c>
-      <c r="N383" t="n">
-        <v>2244</v>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
       </c>
       <c r="O383" t="inlineStr"/>
       <c r="P383" t="inlineStr">

--- a/data/arbeidsfiler/weekly_results_2026.xlsx
+++ b/data/arbeidsfiler/weekly_results_2026.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE392"/>
+  <dimension ref="A1:AE404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28345,10 +28345,8 @@
           <t>16:18</t>
         </is>
       </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="N272" t="n">
+        <v>3</v>
       </c>
       <c r="O272" t="inlineStr">
         <is>
@@ -30919,10 +30917,8 @@
           <t>16:55</t>
         </is>
       </c>
-      <c r="N294" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="N294" t="n">
+        <v>13</v>
       </c>
       <c r="O294" t="inlineStr"/>
       <c r="P294" t="inlineStr">
@@ -31155,10 +31151,8 @@
           <t>17:19</t>
         </is>
       </c>
-      <c r="N296" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="N296" t="n">
+        <v>16</v>
       </c>
       <c r="O296" t="inlineStr"/>
       <c r="P296" t="inlineStr">
@@ -31274,10 +31268,8 @@
           <t>17:22</t>
         </is>
       </c>
-      <c r="N297" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="N297" t="n">
+        <v>17</v>
       </c>
       <c r="O297" t="inlineStr"/>
       <c r="P297" t="inlineStr">
@@ -31510,10 +31502,8 @@
           <t>16:37</t>
         </is>
       </c>
-      <c r="N299" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+      <c r="N299" t="n">
+        <v>19</v>
       </c>
       <c r="O299" t="inlineStr"/>
       <c r="P299" t="inlineStr">
@@ -31980,10 +31970,8 @@
           <t>17:22</t>
         </is>
       </c>
-      <c r="N303" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="N303" t="n">
+        <v>22</v>
       </c>
       <c r="O303" t="inlineStr"/>
       <c r="P303" t="inlineStr">
@@ -32099,10 +32087,8 @@
           <t>17:22</t>
         </is>
       </c>
-      <c r="N304" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="N304" t="n">
+        <v>23</v>
       </c>
       <c r="O304" t="inlineStr"/>
       <c r="P304" t="inlineStr">
@@ -32803,10 +32789,8 @@
           <t>17:58</t>
         </is>
       </c>
-      <c r="N310" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="N310" t="n">
+        <v>31</v>
       </c>
       <c r="O310" t="inlineStr"/>
       <c r="P310" t="inlineStr">
@@ -33858,10 +33842,8 @@
           <t>18:40</t>
         </is>
       </c>
-      <c r="N319" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+      <c r="N319" t="n">
+        <v>45</v>
       </c>
       <c r="O319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
@@ -35028,10 +35010,8 @@
           <t>19:10</t>
         </is>
       </c>
-      <c r="N329" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
+      <c r="N329" t="n">
+        <v>65</v>
       </c>
       <c r="O329" t="inlineStr"/>
       <c r="P329" t="inlineStr">
@@ -35147,10 +35127,8 @@
           <t>19:11</t>
         </is>
       </c>
-      <c r="N330" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+      <c r="N330" t="n">
+        <v>66</v>
       </c>
       <c r="O330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
@@ -35266,10 +35244,8 @@
           <t>18:53</t>
         </is>
       </c>
-      <c r="N331" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="N331" t="n">
+        <v>73</v>
       </c>
       <c r="O331" t="inlineStr"/>
       <c r="P331" t="inlineStr">
@@ -35502,10 +35478,8 @@
           <t>18:58</t>
         </is>
       </c>
-      <c r="N333" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="N333" t="n">
+        <v>80</v>
       </c>
       <c r="O333" t="inlineStr"/>
       <c r="P333" t="inlineStr">
@@ -35621,10 +35595,8 @@
           <t>19:09</t>
         </is>
       </c>
-      <c r="N334" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="N334" t="n">
+        <v>83</v>
       </c>
       <c r="O334" t="inlineStr"/>
       <c r="P334" t="inlineStr">
@@ -36091,10 +36063,8 @@
           <t>19:36</t>
         </is>
       </c>
-      <c r="N338" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
+      <c r="N338" t="n">
+        <v>92</v>
       </c>
       <c r="O338" t="inlineStr"/>
       <c r="P338" t="inlineStr">
@@ -36444,10 +36414,8 @@
           <t>19:50</t>
         </is>
       </c>
-      <c r="N341" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
+      <c r="N341" t="n">
+        <v>104</v>
       </c>
       <c r="O341" t="inlineStr"/>
       <c r="P341" t="inlineStr">
@@ -36563,10 +36531,8 @@
           <t>19:43</t>
         </is>
       </c>
-      <c r="N342" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
+      <c r="N342" t="n">
+        <v>109</v>
       </c>
       <c r="O342" t="inlineStr"/>
       <c r="P342" t="inlineStr">
@@ -37033,10 +36999,8 @@
           <t>19:21</t>
         </is>
       </c>
-      <c r="N346" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="N346" t="n">
+        <v>123</v>
       </c>
       <c r="O346" t="inlineStr"/>
       <c r="P346" t="inlineStr">
@@ -37386,10 +37350,8 @@
           <t>20:02</t>
         </is>
       </c>
-      <c r="N349" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
+      <c r="N349" t="n">
+        <v>131</v>
       </c>
       <c r="O349" t="inlineStr"/>
       <c r="P349" t="inlineStr">
@@ -37622,10 +37584,8 @@
           <t>19:50</t>
         </is>
       </c>
-      <c r="N351" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
+      <c r="N351" t="n">
+        <v>137</v>
       </c>
       <c r="O351" t="inlineStr"/>
       <c r="P351" t="inlineStr">
@@ -37858,10 +37818,8 @@
           <t>19:57</t>
         </is>
       </c>
-      <c r="N353" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
+      <c r="N353" t="n">
+        <v>143</v>
       </c>
       <c r="O353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
@@ -38328,10 +38286,8 @@
           <t>20:31</t>
         </is>
       </c>
-      <c r="N357" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
+      <c r="N357" t="n">
+        <v>173</v>
       </c>
       <c r="O357" t="inlineStr"/>
       <c r="P357" t="inlineStr">
@@ -38564,10 +38520,8 @@
           <t>20:38</t>
         </is>
       </c>
-      <c r="N359" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
+      <c r="N359" t="n">
+        <v>190</v>
       </c>
       <c r="O359" t="inlineStr"/>
       <c r="P359" t="inlineStr">
@@ -38683,10 +38637,8 @@
           <t>20:44</t>
         </is>
       </c>
-      <c r="N360" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
+      <c r="N360" t="n">
+        <v>192</v>
       </c>
       <c r="O360" t="inlineStr"/>
       <c r="P360" t="inlineStr">
@@ -38802,10 +38754,8 @@
           <t>20:51</t>
         </is>
       </c>
-      <c r="N361" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
+      <c r="N361" t="n">
+        <v>201</v>
       </c>
       <c r="O361" t="inlineStr"/>
       <c r="P361" t="inlineStr">
@@ -38921,10 +38871,8 @@
           <t>20:58</t>
         </is>
       </c>
-      <c r="N362" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
+      <c r="N362" t="n">
+        <v>207</v>
       </c>
       <c r="O362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
@@ -39040,10 +38988,8 @@
           <t>20:34</t>
         </is>
       </c>
-      <c r="N363" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
+      <c r="N363" t="n">
+        <v>225</v>
       </c>
       <c r="O363" t="inlineStr"/>
       <c r="P363" t="inlineStr">
@@ -39276,10 +39222,8 @@
           <t>20:54</t>
         </is>
       </c>
-      <c r="N365" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
+      <c r="N365" t="n">
+        <v>235</v>
       </c>
       <c r="O365" t="inlineStr"/>
       <c r="P365" t="inlineStr">
@@ -39629,10 +39573,8 @@
           <t>20:37</t>
         </is>
       </c>
-      <c r="N368" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
+      <c r="N368" t="n">
+        <v>259</v>
       </c>
       <c r="O368" t="inlineStr"/>
       <c r="P368" t="inlineStr">
@@ -39748,10 +39690,8 @@
           <t>21:07</t>
         </is>
       </c>
-      <c r="N369" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
+      <c r="N369" t="n">
+        <v>261</v>
       </c>
       <c r="O369" t="inlineStr"/>
       <c r="P369" t="inlineStr">
@@ -39867,10 +39807,8 @@
           <t>21:17</t>
         </is>
       </c>
-      <c r="N370" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
+      <c r="N370" t="n">
+        <v>294</v>
       </c>
       <c r="O370" t="inlineStr"/>
       <c r="P370" t="inlineStr">
@@ -40337,10 +40275,8 @@
           <t>22:35</t>
         </is>
       </c>
-      <c r="N374" t="inlineStr">
-        <is>
-          <t>388</t>
-        </is>
+      <c r="N374" t="n">
+        <v>388</v>
       </c>
       <c r="O374" t="inlineStr"/>
       <c r="P374" t="inlineStr">
@@ -40573,10 +40509,8 @@
           <t>22:20</t>
         </is>
       </c>
-      <c r="N376" t="inlineStr">
-        <is>
-          <t>459</t>
-        </is>
+      <c r="N376" t="n">
+        <v>459</v>
       </c>
       <c r="O376" t="inlineStr"/>
       <c r="P376" t="inlineStr">
@@ -40692,10 +40626,8 @@
           <t>23:23</t>
         </is>
       </c>
-      <c r="N377" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
+      <c r="N377" t="n">
+        <v>461</v>
       </c>
       <c r="O377" t="inlineStr"/>
       <c r="P377" t="inlineStr">
@@ -41043,10 +40975,8 @@
           <t>24:16</t>
         </is>
       </c>
-      <c r="N380" t="inlineStr">
-        <is>
-          <t>574</t>
-        </is>
+      <c r="N380" t="n">
+        <v>574</v>
       </c>
       <c r="O380" t="inlineStr"/>
       <c r="P380" t="inlineStr">
@@ -41162,10 +41092,8 @@
           <t>24:18</t>
         </is>
       </c>
-      <c r="N381" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
+      <c r="N381" t="n">
+        <v>596</v>
       </c>
       <c r="O381" t="inlineStr"/>
       <c r="P381" t="inlineStr">
@@ -41281,10 +41209,8 @@
           <t>27:43</t>
         </is>
       </c>
-      <c r="N382" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
+      <c r="N382" t="n">
+        <v>976</v>
       </c>
       <c r="O382" t="inlineStr"/>
       <c r="P382" t="inlineStr">
@@ -41400,10 +41326,8 @@
           <t>20:08</t>
         </is>
       </c>
-      <c r="N383" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
+      <c r="N383" t="n">
+        <v>271</v>
       </c>
       <c r="O383" t="inlineStr"/>
       <c r="P383" t="inlineStr">
@@ -42517,6 +42441,1202 @@
       <c r="AE392" t="inlineStr">
         <is>
           <t>10 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>16</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Bislett distanseserie 4- 3K</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Aleksander Amundsen</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr"/>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr"/>
+      <c r="M393" t="inlineStr"/>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr"/>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>Aleksander Amundsen: 10:07</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>racedays-bislett-s2r4-2026-04-19</t>
+        </is>
+      </c>
+      <c r="R393" t="n">
+        <v>1</v>
+      </c>
+      <c r="S393" t="inlineStr"/>
+      <c r="T393" t="inlineStr"/>
+      <c r="U393" t="inlineStr"/>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>Bislett Racedays CSV import</t>
+        </is>
+      </c>
+      <c r="W393" t="inlineStr"/>
+      <c r="X393" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y393" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="Z393" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA393" t="inlineStr"/>
+      <c r="AB393" t="inlineStr"/>
+      <c r="AC393" t="inlineStr"/>
+      <c r="AD393" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE393" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>16</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Bislett distanseserie 4- 3K</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Erik Bjørgum</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr"/>
+      <c r="H394" t="inlineStr"/>
+      <c r="I394" t="inlineStr"/>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr"/>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>Erik Bjørgum: 10:09</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>racedays-bislett-s2r4-2026-04-19</t>
+        </is>
+      </c>
+      <c r="R394" t="n">
+        <v>2</v>
+      </c>
+      <c r="S394" t="inlineStr"/>
+      <c r="T394" t="inlineStr"/>
+      <c r="U394" t="inlineStr"/>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>Bislett Racedays CSV import</t>
+        </is>
+      </c>
+      <c r="W394" t="inlineStr"/>
+      <c r="X394" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y394" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="Z394" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA394" t="inlineStr"/>
+      <c r="AB394" t="inlineStr"/>
+      <c r="AC394" t="inlineStr"/>
+      <c r="AD394" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE394" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>16</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Bislett distanseserie 4- 3K</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Thomas Nordbø Berg</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr"/>
+      <c r="H395" t="inlineStr"/>
+      <c r="I395" t="inlineStr"/>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr"/>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>Thomas Nordbø Berg: 10:16</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>racedays-bislett-s2r4-2026-04-19</t>
+        </is>
+      </c>
+      <c r="R395" t="n">
+        <v>3</v>
+      </c>
+      <c r="S395" t="inlineStr"/>
+      <c r="T395" t="inlineStr"/>
+      <c r="U395" t="inlineStr"/>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>Bislett Racedays CSV import</t>
+        </is>
+      </c>
+      <c r="W395" t="inlineStr"/>
+      <c r="X395" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y395" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="Z395" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA395" t="inlineStr"/>
+      <c r="AB395" t="inlineStr"/>
+      <c r="AC395" t="inlineStr"/>
+      <c r="AD395" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE395" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>16</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Bislett distanseserie 4- 3K</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Sven Thelin</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr"/>
+      <c r="H396" t="inlineStr"/>
+      <c r="I396" t="inlineStr"/>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr"/>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>Sven Thelin: 10:25</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>racedays-bislett-s2r4-2026-04-19</t>
+        </is>
+      </c>
+      <c r="R396" t="n">
+        <v>4</v>
+      </c>
+      <c r="S396" t="inlineStr"/>
+      <c r="T396" t="inlineStr"/>
+      <c r="U396" t="inlineStr"/>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>Bislett Racedays CSV import</t>
+        </is>
+      </c>
+      <c r="W396" t="inlineStr"/>
+      <c r="X396" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y396" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA396" t="inlineStr"/>
+      <c r="AB396" t="inlineStr"/>
+      <c r="AC396" t="inlineStr"/>
+      <c r="AD396" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE396" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>16</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Bislett distanseserie 4- 3K</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Erling Syversveen Lie</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr"/>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr"/>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>Erling Syversveen Lie: 11:21</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>racedays-bislett-s2r4-2026-04-19</t>
+        </is>
+      </c>
+      <c r="R397" t="n">
+        <v>5</v>
+      </c>
+      <c r="S397" t="inlineStr"/>
+      <c r="T397" t="inlineStr"/>
+      <c r="U397" t="inlineStr"/>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>Bislett Racedays CSV import</t>
+        </is>
+      </c>
+      <c r="W397" t="inlineStr"/>
+      <c r="X397" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y397" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="Z397" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA397" t="inlineStr"/>
+      <c r="AB397" t="inlineStr"/>
+      <c r="AC397" t="inlineStr"/>
+      <c r="AD397" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE397" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>16</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Bislett distanseserie 4- 3K</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>K ?pen</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Sissel Hegdahl Oversand</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr"/>
+      <c r="M398" t="inlineStr"/>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr"/>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>Sissel Hegdahl Oversand: 11:55</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>racedays-bislett-s2r4-2026-04-19</t>
+        </is>
+      </c>
+      <c r="R398" t="n">
+        <v>6</v>
+      </c>
+      <c r="S398" t="inlineStr"/>
+      <c r="T398" t="inlineStr"/>
+      <c r="U398" t="inlineStr"/>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>Bislett Racedays CSV import</t>
+        </is>
+      </c>
+      <c r="W398" t="inlineStr"/>
+      <c r="X398" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="Y398" t="inlineStr">
+        <is>
+          <t>K ?pen</t>
+        </is>
+      </c>
+      <c r="Z398" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA398" t="inlineStr"/>
+      <c r="AB398" t="inlineStr"/>
+      <c r="AC398" t="inlineStr"/>
+      <c r="AD398" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="AE398" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>16</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Bislett distanseserie 4- 3K</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>K ?pen</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Ingrid Skomedal Klovning</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr"/>
+      <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr"/>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr"/>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>Ingrid Skomedal Klovning: 12:11</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>racedays-bislett-s2r4-2026-04-19</t>
+        </is>
+      </c>
+      <c r="R399" t="n">
+        <v>7</v>
+      </c>
+      <c r="S399" t="inlineStr"/>
+      <c r="T399" t="inlineStr"/>
+      <c r="U399" t="inlineStr"/>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>Bislett Racedays CSV import</t>
+        </is>
+      </c>
+      <c r="W399" t="inlineStr"/>
+      <c r="X399" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="Y399" t="inlineStr">
+        <is>
+          <t>K ?pen</t>
+        </is>
+      </c>
+      <c r="Z399" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA399" t="inlineStr"/>
+      <c r="AB399" t="inlineStr"/>
+      <c r="AC399" t="inlineStr"/>
+      <c r="AD399" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="AE399" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>16</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Bislett distanseserie 4- 3K</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Sigurd Skomedal Klovning</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr"/>
+      <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr"/>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr"/>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>Sigurd Skomedal Klovning: 12:12</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>racedays-bislett-s2r4-2026-04-19</t>
+        </is>
+      </c>
+      <c r="R400" t="n">
+        <v>8</v>
+      </c>
+      <c r="S400" t="inlineStr"/>
+      <c r="T400" t="inlineStr"/>
+      <c r="U400" t="inlineStr"/>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>Bislett Racedays CSV import</t>
+        </is>
+      </c>
+      <c r="W400" t="inlineStr"/>
+      <c r="X400" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y400" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="Z400" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AA400" t="inlineStr"/>
+      <c r="AB400" t="inlineStr"/>
+      <c r="AC400" t="inlineStr"/>
+      <c r="AD400" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE400" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B401" t="n">
+        <v>16</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Bislett distanseserie 4- 3K</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Christian Lillebo</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr"/>
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr"/>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr"/>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>Christian Lillebo: 12:25</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>racedays-bislett-s2r4-2026-04-19</t>
+        </is>
+      </c>
+      <c r="R401" t="n">
+        <v>9</v>
+      </c>
+      <c r="S401" t="inlineStr"/>
+      <c r="T401" t="inlineStr"/>
+      <c r="U401" t="inlineStr"/>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>Bislett Racedays CSV import</t>
+        </is>
+      </c>
+      <c r="W401" t="inlineStr"/>
+      <c r="X401" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y401" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="Z401" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA401" t="inlineStr"/>
+      <c r="AB401" t="inlineStr"/>
+      <c r="AC401" t="inlineStr"/>
+      <c r="AD401" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE401" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B402" t="n">
+        <v>16</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Bislett distanseserie 4- 3K</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Sveinung Nersten</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr"/>
+      <c r="H402" t="inlineStr"/>
+      <c r="I402" t="inlineStr"/>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr"/>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>Sveinung Nersten: 12:39</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>racedays-bislett-s2r4-2026-04-19</t>
+        </is>
+      </c>
+      <c r="R402" t="n">
+        <v>10</v>
+      </c>
+      <c r="S402" t="inlineStr"/>
+      <c r="T402" t="inlineStr"/>
+      <c r="U402" t="inlineStr"/>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>Bislett Racedays CSV import</t>
+        </is>
+      </c>
+      <c r="W402" t="inlineStr"/>
+      <c r="X402" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y402" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="Z402" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA402" t="inlineStr"/>
+      <c r="AB402" t="inlineStr"/>
+      <c r="AC402" t="inlineStr"/>
+      <c r="AD402" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE402" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B403" t="n">
+        <v>16</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Bislett distanseserie 4- 3K</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Fredrik Camilo Halsbog</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="inlineStr"/>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr"/>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>Fredrik Camilo Halsbog: DNF</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>racedays-bislett-s2r4-2026-04-19</t>
+        </is>
+      </c>
+      <c r="R403" t="n">
+        <v>11</v>
+      </c>
+      <c r="S403" t="inlineStr"/>
+      <c r="T403" t="inlineStr"/>
+      <c r="U403" t="inlineStr"/>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>Bislett Racedays CSV import</t>
+        </is>
+      </c>
+      <c r="W403" t="inlineStr"/>
+      <c r="X403" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y403" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="Z403" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+      <c r="AA403" t="inlineStr"/>
+      <c r="AB403" t="inlineStr"/>
+      <c r="AC403" t="inlineStr"/>
+      <c r="AD403" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE403" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B404" t="n">
+        <v>16</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Bislett distanseserie 4- 3K</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>3000 m</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Kristian Frøyen</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="inlineStr"/>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr"/>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>Kristian Frøyen: DNF</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>racedays-bislett-s2r4-2026-04-19</t>
+        </is>
+      </c>
+      <c r="R404" t="n">
+        <v>12</v>
+      </c>
+      <c r="S404" t="inlineStr"/>
+      <c r="T404" t="inlineStr"/>
+      <c r="U404" t="inlineStr"/>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>Bislett Racedays CSV import</t>
+        </is>
+      </c>
+      <c r="W404" t="inlineStr"/>
+      <c r="X404" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Y404" t="inlineStr">
+        <is>
+          <t>M ?pen</t>
+        </is>
+      </c>
+      <c r="Z404" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+      <c r="AA404" t="inlineStr"/>
+      <c r="AB404" t="inlineStr"/>
+      <c r="AC404" t="inlineStr"/>
+      <c r="AD404" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="AE404" t="inlineStr">
+        <is>
+          <t>3000 m</t>
         </is>
       </c>
     </row>
